--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="157">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -85,6 +88,108 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1161 София Шипченски проход</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1145 София Вапцаров</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1136 Димитровград Д. Благоев</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1194 Дунавци</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1914 О5, Плевен</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1908 О5 Стара Загора</t>
+  </si>
+  <si>
+    <t>1149 Кюстендил Николичевски път</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1151 Пловдив, бул. България</t>
+  </si>
+  <si>
+    <t>1183 София Чепинци</t>
+  </si>
+  <si>
     <t>78970110027720084</t>
   </si>
   <si>
@@ -118,64 +223,250 @@
     <t>78970110027720142</t>
   </si>
   <si>
+    <t>78970110027720159</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2Л EKO ЛЯTHA TEЧHOCT</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>13:39</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>12:40</t>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>13:39:00</t>
+  </si>
+  <si>
+    <t>08:07:00</t>
+  </si>
+  <si>
+    <t>19:53:00</t>
+  </si>
+  <si>
+    <t>13:51:00</t>
+  </si>
+  <si>
+    <t>09:38:00</t>
+  </si>
+  <si>
+    <t>12:45:00</t>
+  </si>
+  <si>
+    <t>08:52:00</t>
+  </si>
+  <si>
+    <t>14:32:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>15:13:00</t>
+  </si>
+  <si>
+    <t>17:25:00</t>
+  </si>
+  <si>
+    <t>14:48:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>17:59:00</t>
+  </si>
+  <si>
+    <t>10:58:00</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>20:26:00</t>
+  </si>
+  <si>
+    <t>19:48:00</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>13:49:00</t>
+  </si>
+  <si>
+    <t>14:58:00</t>
+  </si>
+  <si>
+    <t>14:29:00</t>
+  </si>
+  <si>
+    <t>10:24:00</t>
+  </si>
+  <si>
+    <t>09:28:00</t>
+  </si>
+  <si>
+    <t>17:47:00</t>
+  </si>
+  <si>
+    <t>15:22:00</t>
+  </si>
+  <si>
+    <t>11:07:00</t>
+  </si>
+  <si>
+    <t>12:50:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>3231292813 3231292813</t>
+  </si>
+  <si>
+    <t>3231301165 3231301165</t>
+  </si>
+  <si>
+    <t>3231371807 3231371807</t>
+  </si>
+  <si>
+    <t>3231363244 3231363244</t>
+  </si>
+  <si>
+    <t>3231546188 3231546188</t>
+  </si>
+  <si>
+    <t>3231546366 3231546366</t>
+  </si>
+  <si>
+    <t>3231540630 3231540630</t>
+  </si>
+  <si>
+    <t>3231645441 3231645441</t>
+  </si>
+  <si>
+    <t>3231663761 3231663761</t>
+  </si>
+  <si>
+    <t>3231726078 3231726078</t>
+  </si>
+  <si>
+    <t>3231767086 3231767086</t>
+  </si>
+  <si>
+    <t>3231826652 3231826652</t>
+  </si>
+  <si>
+    <t>3231824580 3231824580</t>
+  </si>
+  <si>
+    <t>3231822871 3231822871</t>
+  </si>
+  <si>
+    <t>3231818960 3231818960</t>
+  </si>
+  <si>
+    <t>3231915341 3231915341</t>
+  </si>
+  <si>
+    <t>3232018114 3232018114</t>
+  </si>
+  <si>
+    <t>3232105421 3232105421</t>
+  </si>
+  <si>
+    <t>3232160220 3232160220</t>
+  </si>
+  <si>
+    <t>3232161120 3232161120</t>
+  </si>
+  <si>
+    <t>3232146756 3232146756</t>
+  </si>
+  <si>
+    <t>3232150049 3232150049</t>
+  </si>
+  <si>
+    <t>3232145329 3232145329</t>
+  </si>
+  <si>
+    <t>3232153581 3232153581</t>
+  </si>
+  <si>
+    <t>3232186770 3232186770</t>
+  </si>
+  <si>
+    <t>3232193397 3232193397</t>
+  </si>
+  <si>
+    <t>3232307313 3232307313</t>
+  </si>
+  <si>
+    <t>3232302503 3232302503</t>
+  </si>
+  <si>
+    <t>3232341009 3232341009</t>
+  </si>
+  <si>
+    <t>3232372570 3232372570</t>
+  </si>
+  <si>
+    <t>3232420232 3232420232</t>
+  </si>
+  <si>
+    <t>3232472224 3232472224</t>
+  </si>
+  <si>
+    <t>3232530054 3232530054</t>
+  </si>
+  <si>
+    <t>3232525394 3232525394</t>
+  </si>
+  <si>
+    <t>3232585970 3232585970</t>
+  </si>
+  <si>
+    <t>3232638200 3232638200</t>
+  </si>
+  <si>
+    <t>3232622156 3232622156</t>
+  </si>
+  <si>
+    <t>3232628022 3232628022</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЖИ ТИ ЕЙ ПЕТРОЛИУМ</t>
@@ -599,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -608,16 +899,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -657,835 +949,1857 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1158</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F2">
         <v>51.15</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2">
         <v>1.64</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>83.89</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>92.06999999999999</v>
       </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>76</v>
       </c>
       <c r="M2">
-        <v>89244</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1101</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
       </c>
       <c r="C3">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F3">
         <v>18.05</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3">
         <v>0.84</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>15.16</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.84</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>15.16</v>
       </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>77</v>
       </c>
       <c r="M3">
-        <v>151498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1160</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>39.82</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4">
         <v>1.64</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>65.3</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>71.68000000000001</v>
       </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>78</v>
       </c>
       <c r="M4">
-        <v>262321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1161</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
       </c>
       <c r="C5">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4.34</v>
+        <v>36.41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
       </c>
       <c r="H5">
-        <v>4.34</v>
+        <v>1.4</v>
       </c>
       <c r="I5" s="1">
-        <v>4.34</v>
+        <v>50.97</v>
       </c>
       <c r="J5">
-        <v>4.34</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+        <v>1.52</v>
+      </c>
+      <c r="K5" s="1">
+        <v>55.34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
       </c>
       <c r="M5">
-        <v>80537</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>1161</v>
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F6">
-        <v>36.41</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.4</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>50.97</v>
+        <v>4.34</v>
       </c>
       <c r="I6" s="1">
-        <v>1.52</v>
+        <v>4.34</v>
       </c>
       <c r="J6">
-        <v>55.34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+        <v>4.34</v>
+      </c>
+      <c r="K6" s="1">
+        <v>4.34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>79</v>
       </c>
       <c r="M6">
-        <v>80537</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1172</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
       </c>
       <c r="C7">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F7">
         <v>60</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7">
         <v>1.64</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>98.40000000000001</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.8</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>108</v>
       </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>155525</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>1195</v>
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>61.87</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8">
         <v>1.64</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>101.47</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.82</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>112.6</v>
       </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>81</v>
       </c>
       <c r="M8">
-        <v>226080</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>1903</v>
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
       </c>
       <c r="C9">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F9">
         <v>17.55</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9">
         <v>0.83</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>14.57</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>0.83</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>14.57</v>
       </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>82</v>
       </c>
       <c r="M9">
-        <v>116099</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>1145</v>
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F10">
         <v>34.69</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10">
         <v>0.83</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>28.79</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>0.83</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>28.79</v>
       </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>83</v>
       </c>
       <c r="M10">
-        <v>83656</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>1131</v>
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
       </c>
       <c r="C11">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>67.90000000000001</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11">
         <v>1.63</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>110.68</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.79</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>121.54</v>
       </c>
-      <c r="K11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>84</v>
       </c>
       <c r="M11">
-        <v>277091</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>1136</v>
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F12">
         <v>44.69</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12">
         <v>1.63</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>72.84</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.79</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>80</v>
       </c>
-      <c r="K12" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="L12" t="s">
+        <v>85</v>
       </c>
       <c r="M12">
-        <v>842440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13">
-        <v>1902</v>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
       </c>
       <c r="C13">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>37.99</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13">
         <v>1.62</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>61.54</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.79</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>68</v>
       </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
+      <c r="L13" t="s">
+        <v>86</v>
       </c>
       <c r="M13">
-        <v>82277</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>1147</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <v>49.56</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14">
         <v>1.62</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>80.29000000000001</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.78</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>88.22</v>
       </c>
-      <c r="K14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>87</v>
       </c>
       <c r="M14">
-        <v>180738</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15">
-        <v>1158</v>
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F15">
         <v>49.4</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15">
         <v>1.62</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>80.03</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.78</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>87.93000000000001</v>
       </c>
-      <c r="K15" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>88</v>
       </c>
       <c r="M15">
-        <v>95404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>1160</v>
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F16">
         <v>35.42</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16">
         <v>1.62</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>57.38</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.78</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>63.05</v>
       </c>
-      <c r="K16" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="L16" t="s">
+        <v>89</v>
       </c>
       <c r="M16">
-        <v>157156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
-        <v>1903</v>
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F17">
         <v>36.15</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>29.28</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>29.28</v>
       </c>
-      <c r="K17" t="s">
-        <v>52</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="L17" t="s">
+        <v>90</v>
       </c>
       <c r="M17">
-        <v>118688</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18">
-        <v>1903</v>
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
       </c>
       <c r="C18">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>70.61</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18">
         <v>1.61</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>113.68</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.76</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>124.27</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>56.43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19">
+        <v>1.61</v>
+      </c>
+      <c r="I19" s="1">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="J19">
+        <v>1.75</v>
+      </c>
+      <c r="K19" s="1">
+        <v>98.75</v>
+      </c>
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20">
+        <v>40.94</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20">
+        <v>1.59</v>
+      </c>
+      <c r="I20" s="1">
+        <v>65.09</v>
+      </c>
+      <c r="J20">
+        <v>1.77</v>
+      </c>
+      <c r="K20" s="1">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21">
+        <v>20.84</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21">
+        <v>1.59</v>
+      </c>
+      <c r="I21" s="1">
+        <v>33.14</v>
+      </c>
+      <c r="J21">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="1">
+        <v>36.47</v>
+      </c>
+      <c r="L21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22">
+        <v>57.81</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22">
+        <v>1.59</v>
+      </c>
+      <c r="I22" s="1">
+        <v>91.92</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22" s="1">
+        <v>101.17</v>
+      </c>
+      <c r="L22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23">
+        <v>58.65</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23">
+        <v>1.59</v>
+      </c>
+      <c r="I23" s="1">
+        <v>93.25</v>
+      </c>
+      <c r="J23">
+        <v>1.76</v>
+      </c>
+      <c r="K23" s="1">
+        <v>103.22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24">
+        <v>38.53</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24">
+        <v>1.59</v>
+      </c>
+      <c r="I24" s="1">
+        <v>61.26</v>
+      </c>
+      <c r="J24">
+        <v>1.76</v>
+      </c>
+      <c r="K24" s="1">
+        <v>67.81</v>
+      </c>
+      <c r="L24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25">
+        <v>15.8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25">
+        <v>1.59</v>
+      </c>
+      <c r="I25" s="1">
+        <v>25.12</v>
+      </c>
+      <c r="J25">
+        <v>1.75</v>
+      </c>
+      <c r="K25" s="1">
+        <v>27.65</v>
+      </c>
+      <c r="L25" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26">
+        <v>34.13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26">
+        <v>0.79</v>
+      </c>
+      <c r="I26" s="1">
+        <v>26.96</v>
+      </c>
+      <c r="J26">
+        <v>0.79</v>
+      </c>
+      <c r="K26" s="1">
+        <v>26.96</v>
+      </c>
+      <c r="L26" t="s">
+        <v>99</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27">
+        <v>51.98</v>
+      </c>
+      <c r="G27" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27">
+        <v>1.46</v>
+      </c>
+      <c r="I27" s="1">
+        <v>75.89</v>
+      </c>
+      <c r="J27">
+        <v>1.57</v>
+      </c>
+      <c r="K27" s="1">
+        <v>81.61</v>
+      </c>
+      <c r="L27" t="s">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28">
+        <v>41.91</v>
+      </c>
+      <c r="G28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28">
+        <v>1.59</v>
+      </c>
+      <c r="I28" s="1">
+        <v>66.64</v>
+      </c>
+      <c r="J28">
+        <v>1.75</v>
+      </c>
+      <c r="K28" s="1">
+        <v>73.34</v>
+      </c>
+      <c r="L28" t="s">
+        <v>101</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>119631</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="3" t="s">
+      <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29">
+        <v>22.42</v>
+      </c>
+      <c r="G29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29">
+        <v>0.79</v>
+      </c>
+      <c r="I29" s="1">
+        <v>17.71</v>
+      </c>
+      <c r="J29">
+        <v>0.79</v>
+      </c>
+      <c r="K29" s="1">
+        <v>17.71</v>
+      </c>
+      <c r="L29" t="s">
+        <v>102</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="4" t="s">
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30">
+        <v>52.24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30">
+        <v>1.59</v>
+      </c>
+      <c r="I30" s="1">
+        <v>83.06</v>
+      </c>
+      <c r="J30">
+        <v>1.73</v>
+      </c>
+      <c r="K30" s="1">
+        <v>90.38</v>
+      </c>
+      <c r="L30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31">
+        <v>33.58</v>
+      </c>
+      <c r="G31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31">
+        <v>0.79</v>
+      </c>
+      <c r="I31" s="1">
+        <v>26.53</v>
+      </c>
+      <c r="J31">
+        <v>0.79</v>
+      </c>
+      <c r="K31" s="1">
+        <v>26.53</v>
+      </c>
+      <c r="L31" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32">
+        <v>15.83</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I32" s="1">
+        <v>12.82</v>
+      </c>
+      <c r="J32">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K32" s="1">
+        <v>12.82</v>
+      </c>
+      <c r="L32" t="s">
+        <v>105</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33">
+        <v>1.46</v>
+      </c>
+      <c r="I33" s="1">
+        <v>14.6</v>
+      </c>
+      <c r="J33">
+        <v>1.57</v>
+      </c>
+      <c r="K33" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="L33" t="s">
+        <v>106</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34">
+        <v>39.82</v>
+      </c>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34">
+        <v>1.59</v>
+      </c>
+      <c r="I34" s="1">
+        <v>63.31</v>
+      </c>
+      <c r="J34">
+        <v>1.74</v>
+      </c>
+      <c r="K34" s="1">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="L34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35">
+        <v>22.47</v>
+      </c>
+      <c r="G35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35">
+        <v>0.78</v>
+      </c>
+      <c r="I35" s="1">
+        <v>17.53</v>
+      </c>
+      <c r="J35">
+        <v>0.78</v>
+      </c>
+      <c r="K35" s="1">
+        <v>17.53</v>
+      </c>
+      <c r="L35" t="s">
+        <v>108</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C36">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36">
+        <v>39.71</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36">
+        <v>1.59</v>
+      </c>
+      <c r="I36" s="1">
+        <v>63.14</v>
+      </c>
+      <c r="J36">
+        <v>1.71</v>
+      </c>
+      <c r="K36" s="1">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="L36" t="s">
+        <v>109</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37">
+        <v>35.92</v>
+      </c>
+      <c r="G37" t="s">
+        <v>74</v>
+      </c>
+      <c r="H37">
+        <v>0.77</v>
+      </c>
+      <c r="I37" s="1">
+        <v>27.66</v>
+      </c>
+      <c r="J37">
+        <v>0.77</v>
+      </c>
+      <c r="K37" s="1">
+        <v>27.66</v>
+      </c>
+      <c r="L37" t="s">
+        <v>95</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="6">
-        <v>568.41</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="D38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38">
+        <v>22.74</v>
+      </c>
+      <c r="G38" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38">
+        <v>0.77</v>
+      </c>
+      <c r="I38" s="1">
+        <v>17.51</v>
+      </c>
+      <c r="J38">
+        <v>0.77</v>
+      </c>
+      <c r="K38" s="1">
+        <v>17.51</v>
+      </c>
+      <c r="L38" t="s">
+        <v>110</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39">
         <v>11</v>
       </c>
-      <c r="D23" s="7">
-        <v>1.6282</v>
-      </c>
-      <c r="E23" s="6">
-        <v>925.5</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1017.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="5" t="s">
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39">
+        <v>38.22</v>
+      </c>
+      <c r="G39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39">
+        <v>1.48</v>
+      </c>
+      <c r="I39" s="1">
+        <v>56.57</v>
+      </c>
+      <c r="J39">
+        <v>1.57</v>
+      </c>
+      <c r="K39" s="1">
+        <v>60.01</v>
+      </c>
+      <c r="L39" t="s">
+        <v>111</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="6">
-        <v>106.44</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40">
+        <v>36.53</v>
+      </c>
+      <c r="G40" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40">
+        <v>1.58</v>
+      </c>
+      <c r="I40" s="1">
+        <v>57.72</v>
+      </c>
+      <c r="J40">
+        <v>1.69</v>
+      </c>
+      <c r="K40" s="1">
+        <v>61.74</v>
+      </c>
+      <c r="L40" t="s">
+        <v>112</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="6">
+        <v>1067.62</v>
+      </c>
+      <c r="C45" s="6">
+        <v>23</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1.6111</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1720</v>
+      </c>
+      <c r="F45" s="6">
+        <v>1887.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="6">
+        <v>293.53</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.799</v>
+      </c>
+      <c r="E46" s="6">
+        <v>234.52</v>
+      </c>
+      <c r="F46" s="6">
+        <v>234.52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="6">
+        <v>136.61</v>
+      </c>
+      <c r="C47" s="6">
         <v>4</v>
       </c>
-      <c r="D24" s="7">
-        <v>0.8249</v>
-      </c>
-      <c r="E24" s="6">
-        <v>87.8</v>
-      </c>
-      <c r="F24" s="6">
-        <v>87.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="6">
-        <v>36.41</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="D47" s="7">
+        <v>1.4496</v>
+      </c>
+      <c r="E47" s="6">
+        <v>198.03</v>
+      </c>
+      <c r="F47" s="6">
+        <v>212.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="6">
         <v>1</v>
       </c>
-      <c r="D25" s="7">
-        <v>1.3999</v>
-      </c>
-      <c r="E25" s="6">
-        <v>50.97</v>
-      </c>
-      <c r="F25" s="6">
-        <v>55.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="6">
+      <c r="C48" s="6">
         <v>1</v>
       </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="D48" s="7">
         <v>4.34</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E48" s="6">
         <v>4.34</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F48" s="6">
         <v>4.34</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="9">
-        <v>712.26</v>
-      </c>
-      <c r="C27" s="9">
-        <v>17</v>
-      </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="9">
-        <v>1068.61</v>
-      </c>
-      <c r="F27" s="9">
-        <v>1164.84</v>
+    <row r="49" spans="1:6">
+      <c r="A49" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="9">
+        <v>1498.76</v>
+      </c>
+      <c r="C49" s="9">
+        <v>39</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="9">
+        <v>2156.89</v>
+      </c>
+      <c r="F49" s="9">
+        <v>2339.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -520,7 +520,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,12 +530,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,17 +579,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="155">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -106,67 +115,88 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Монтана</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>Радиново</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>София Ломско шосе</t>
-  </si>
-  <si>
-    <t>Кулата Струма</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>София Сливница</t>
-  </si>
-  <si>
-    <t>Стара Загора</t>
-  </si>
-  <si>
-    <t>София Ботевградско шосе</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
-  </si>
-  <si>
-    <t>София К. Величков</t>
-  </si>
-  <si>
-    <t>София Бояна</t>
-  </si>
-  <si>
-    <t>Кулата</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>София Вапцаров</t>
-  </si>
-  <si>
-    <t>София Княжево</t>
-  </si>
-  <si>
-    <t>Димитровград</t>
-  </si>
-  <si>
-    <t>София Черни връх</t>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1134 Монтана</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1139 София Ломско шосе</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1121 София Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1908 О5 Стара Загора</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1165 София К. Величков</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1145 София Вапцаров</t>
+  </si>
+  <si>
+    <t>1904 София, О5 Княжево</t>
+  </si>
+  <si>
+    <t>1136 Димитровград Д. Благоев</t>
+  </si>
+  <si>
+    <t>1117 София Черни Връх</t>
+  </si>
+  <si>
+    <t>1189 Дупница</t>
+  </si>
+  <si>
+    <t>1922 Kardzhali Belomorski</t>
+  </si>
+  <si>
+    <t>1151 Пловдив, бул. България</t>
   </si>
   <si>
     <t>78970110027720092</t>
@@ -181,18 +211,18 @@
     <t>78970110027720076</t>
   </si>
   <si>
+    <t>78970110027720035</t>
+  </si>
+  <si>
     <t>78970110027720126</t>
   </si>
   <si>
-    <t>78970110027720035</t>
+    <t>78970110027720084</t>
   </si>
   <si>
     <t>78970110027720241</t>
   </si>
   <si>
-    <t>78970110027720084</t>
-  </si>
-  <si>
     <t>78970110027720233</t>
   </si>
   <si>
@@ -208,100 +238,229 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-01 09:52:46</t>
-  </si>
-  <si>
-    <t>2026-06-02 16:23:59</t>
-  </si>
-  <si>
-    <t>2026-06-03 18:03:47</t>
-  </si>
-  <si>
-    <t>2026-06-04 09:19:25</t>
-  </si>
-  <si>
-    <t>2026-06-06 11:48:24</t>
-  </si>
-  <si>
-    <t>2026-06-06 12:39:43</t>
-  </si>
-  <si>
-    <t>2026-06-06 16:52:09</t>
-  </si>
-  <si>
-    <t>2026-06-07 10:07:35</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:25:17</t>
-  </si>
-  <si>
-    <t>2026-06-08 17:40:02</t>
-  </si>
-  <si>
-    <t>2026-06-09 08:55:55</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:14:15</t>
-  </si>
-  <si>
-    <t>2026-06-10 15:04:02</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:57:53</t>
-  </si>
-  <si>
-    <t>2026-06-10 19:08:33</t>
-  </si>
-  <si>
-    <t>2026-06-12 14:04:05</t>
-  </si>
-  <si>
-    <t>2026-06-12 15:32:31</t>
-  </si>
-  <si>
-    <t>2026-06-13 14:42:25</t>
-  </si>
-  <si>
-    <t>2026-06-13 19:46:55</t>
-  </si>
-  <si>
-    <t>2026-06-15 09:52:39</t>
-  </si>
-  <si>
-    <t>2026-06-15 09:52:40</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:01:42</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:45:46</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:07:33</t>
-  </si>
-  <si>
-    <t>2026-06-19 14:49:21</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:25:05</t>
-  </si>
-  <si>
-    <t>2026-06-20 15:06:45</t>
-  </si>
-  <si>
-    <t>2026-06-21 21:14:20</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:12:57</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:56:29</t>
-  </si>
-  <si>
-    <t>2026-06-24 09:30:55</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:38:01</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:52:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>18:03:00</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>16:52:00</t>
+  </si>
+  <si>
+    <t>11:48:00</t>
+  </si>
+  <si>
+    <t>12:39:00</t>
+  </si>
+  <si>
+    <t>10:07:00</t>
+  </si>
+  <si>
+    <t>17:40:00</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
+  </si>
+  <si>
+    <t>13:14:00</t>
+  </si>
+  <si>
+    <t>19:08:00</t>
+  </si>
+  <si>
+    <t>15:03:00</t>
+  </si>
+  <si>
+    <t>16:57:00</t>
+  </si>
+  <si>
+    <t>15:32:00</t>
+  </si>
+  <si>
+    <t>14:03:00</t>
+  </si>
+  <si>
+    <t>19:46:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>09:51:00</t>
+  </si>
+  <si>
+    <t>11:46:00</t>
+  </si>
+  <si>
+    <t>11:01:00</t>
+  </si>
+  <si>
+    <t>09:08:00</t>
+  </si>
+  <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>15:25:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>21:14:00</t>
+  </si>
+  <si>
+    <t>10:09:00</t>
+  </si>
+  <si>
+    <t>09:29:00</t>
+  </si>
+  <si>
+    <t>15:31:00</t>
+  </si>
+  <si>
+    <t>07:56:00</t>
+  </si>
+  <si>
+    <t>22:14:00</t>
+  </si>
+  <si>
+    <t>18:11:00</t>
+  </si>
+  <si>
+    <t>15:49:00</t>
+  </si>
+  <si>
+    <t>08:02:00</t>
+  </si>
+  <si>
+    <t>16:08:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>3232703575 3232703575</t>
+  </si>
+  <si>
+    <t>3232759459 3232759459</t>
+  </si>
+  <si>
+    <t>3232785098 3232785098</t>
+  </si>
+  <si>
+    <t>3232851901 3232851901</t>
+  </si>
+  <si>
+    <t>3232967738 3232967738</t>
+  </si>
+  <si>
+    <t>3232947571 3232947571</t>
+  </si>
+  <si>
+    <t>3232960898 3232960898</t>
+  </si>
+  <si>
+    <t>3233002442 3233002442</t>
+  </si>
+  <si>
+    <t>3233057121 3233057121</t>
+  </si>
+  <si>
+    <t>3233034873 3233034873</t>
+  </si>
+  <si>
+    <t>3233081299 3233081299</t>
+  </si>
+  <si>
+    <t>3233097496 3233097496</t>
+  </si>
+  <si>
+    <t>3233156635 3233156635</t>
+  </si>
+  <si>
+    <t>3233143866 3233143866</t>
+  </si>
+  <si>
+    <t>3233146375 3233146375</t>
+  </si>
+  <si>
+    <t>3233233170 3233233170</t>
+  </si>
+  <si>
+    <t>3233255829 3233255829</t>
+  </si>
+  <si>
+    <t>3233304582 3233304582</t>
+  </si>
+  <si>
+    <t>3233308622 3233308622</t>
+  </si>
+  <si>
+    <t>3233383756 3233383756</t>
+  </si>
+  <si>
+    <t>3233410645 3233410645</t>
+  </si>
+  <si>
+    <t>3233429386 3233429386</t>
+  </si>
+  <si>
+    <t>3233522231 3233522231</t>
+  </si>
+  <si>
+    <t>3233580071 3233580071</t>
+  </si>
+  <si>
+    <t>3233572875 3233572875</t>
+  </si>
+  <si>
+    <t>3233633577 3233633577</t>
+  </si>
+  <si>
+    <t>3233685662 3233685662</t>
+  </si>
+  <si>
+    <t>3233760692 3233760692</t>
+  </si>
+  <si>
+    <t>3233806001 3233806001</t>
+  </si>
+  <si>
+    <t>3233832332 3233832332</t>
+  </si>
+  <si>
+    <t>3233783635 3233783635</t>
+  </si>
+  <si>
+    <t>3233873364 3233873364</t>
+  </si>
+  <si>
+    <t>3233959726 3233959726</t>
+  </si>
+  <si>
+    <t>3233952964 3233952964</t>
+  </si>
+  <si>
+    <t>3234052097 3234052097</t>
+  </si>
+  <si>
+    <t>3234105003 3234105003</t>
+  </si>
+  <si>
+    <t>3234107742 3234107742</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЖИ ТИ ЕЙ ПЕТРОЛИУМ</t>
@@ -719,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -728,14 +887,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -769,1238 +931,1799 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>33.62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2">
         <v>1.57</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>52.78</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>56.82</v>
       </c>
-      <c r="K2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F3">
         <v>58.54</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3">
         <v>1.56</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>91.31999999999999</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>98.93000000000001</v>
       </c>
-      <c r="K3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F4">
         <v>27.27</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4">
         <v>1.56</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>42.54</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.71</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>46.63</v>
       </c>
-      <c r="K4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F5">
         <v>33.53</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5">
         <v>1.54</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>51.64</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.69</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>56.67</v>
       </c>
-      <c r="K5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6">
+        <v>24.78</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6">
+        <v>0.73</v>
+      </c>
+      <c r="I6" s="1">
+        <v>18.09</v>
+      </c>
+      <c r="J6">
+        <v>0.73</v>
+      </c>
+      <c r="K6" s="1">
+        <v>18.09</v>
+      </c>
+      <c r="L6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6">
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7">
         <v>72.48</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7">
         <v>1.53</v>
       </c>
-      <c r="H6">
+      <c r="I7" s="1">
         <v>110.89</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J7">
         <v>1.66</v>
       </c>
-      <c r="J6">
+      <c r="K7" s="1">
         <v>120.32</v>
       </c>
-      <c r="K6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7">
+      <c r="L7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7">
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8">
         <v>51.23</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8">
         <v>1.53</v>
       </c>
-      <c r="H7">
+      <c r="I8" s="1">
         <v>78.38</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J8">
         <v>1.66</v>
       </c>
-      <c r="J7">
+      <c r="K8" s="1">
         <v>85.04000000000001</v>
       </c>
-      <c r="K7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8">
-        <v>24.78</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H8">
-        <v>18.09</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="J8">
-        <v>18.09</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>25.86</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9">
         <v>0.73</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>18.88</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>0.73</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>18.88</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10">
+      <c r="F10">
+        <v>6.13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10">
+        <v>1.53</v>
+      </c>
+      <c r="I10" s="1">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="J10">
+        <v>1.63</v>
+      </c>
+      <c r="K10" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
         <v>4</v>
       </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10">
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11">
         <v>38.26</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11">
         <v>1.53</v>
       </c>
-      <c r="H10">
+      <c r="I11" s="1">
         <v>58.54</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J11">
         <v>1.64</v>
       </c>
-      <c r="J10">
+      <c r="K11" s="1">
         <v>62.75</v>
       </c>
-      <c r="K10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11">
-        <v>6.13</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H11">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="J11">
-        <v>9.99</v>
-      </c>
-      <c r="K11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F12">
         <v>49.44</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12">
         <v>1.51</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>74.65000000000001</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.66</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>82.06999999999999</v>
       </c>
-      <c r="K12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F13">
         <v>42.06</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13">
         <v>1.51</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>63.51</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.64</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>68.98</v>
       </c>
-      <c r="K13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14">
+        <v>40.36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14">
+        <v>1.51</v>
+      </c>
+      <c r="I14" s="1">
+        <v>60.94</v>
+      </c>
+      <c r="J14">
+        <v>1.63</v>
+      </c>
+      <c r="K14" s="1">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14">
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15">
         <v>35.77</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15">
         <v>1.51</v>
       </c>
-      <c r="H14">
+      <c r="I15" s="1">
         <v>54.01</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J15">
         <v>1.63</v>
       </c>
-      <c r="J14">
+      <c r="K15" s="1">
         <v>58.31</v>
       </c>
-      <c r="K14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16">
         <v>4</v>
       </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15">
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16">
         <v>57.14</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16">
         <v>1.51</v>
       </c>
-      <c r="H15">
+      <c r="I16" s="1">
         <v>86.28</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J16">
         <v>1.65</v>
       </c>
-      <c r="J15">
+      <c r="K16" s="1">
         <v>94.28</v>
       </c>
-      <c r="K15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16">
-        <v>40.36</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H16">
-        <v>60.94</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="J16">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="K16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C17">
         <v>9</v>
       </c>
       <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17">
+        <v>33.97</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17">
+        <v>1.44</v>
+      </c>
+      <c r="I17" s="1">
+        <v>48.92</v>
+      </c>
+      <c r="J17">
+        <v>1.56</v>
+      </c>
+      <c r="K17" s="1">
+        <v>52.99</v>
+      </c>
+      <c r="L17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
         <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17">
-        <v>63.25</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H17">
-        <v>95.51000000000001</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J17">
-        <v>101.2</v>
-      </c>
-      <c r="K17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
       </c>
       <c r="C18">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F18">
-        <v>33.97</v>
-      </c>
-      <c r="G18" s="1">
+        <v>63.25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18">
+        <v>1.51</v>
+      </c>
+      <c r="I18" s="1">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="J18">
+        <v>1.6</v>
+      </c>
+      <c r="K18" s="1">
+        <v>101.2</v>
+      </c>
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19">
+        <v>26.31</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19">
         <v>1.44</v>
       </c>
-      <c r="H18">
-        <v>48.92</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="I19" s="1">
+        <v>37.89</v>
+      </c>
+      <c r="J19">
         <v>1.56</v>
       </c>
-      <c r="J18">
-        <v>52.99</v>
-      </c>
-      <c r="K18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19">
+      <c r="K19" s="1">
+        <v>41.04</v>
+      </c>
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20">
         <v>3</v>
       </c>
-      <c r="D19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19">
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20">
         <v>20.82</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20">
         <v>0.68</v>
       </c>
-      <c r="H19">
+      <c r="I20" s="1">
         <v>14.16</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J20">
         <v>0.68</v>
       </c>
-      <c r="J19">
+      <c r="K20" s="1">
         <v>14.16</v>
       </c>
-      <c r="K19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20">
-        <v>26.31</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H20">
-        <v>37.89</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J20">
-        <v>41.04</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C21">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F21">
-        <v>11.03</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.68</v>
+        <v>11.77</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
       </c>
       <c r="H21">
-        <v>7.5</v>
+        <v>1.44</v>
       </c>
       <c r="I21" s="1">
-        <v>0.68</v>
+        <v>16.95</v>
       </c>
       <c r="J21">
-        <v>7.5</v>
-      </c>
-      <c r="K21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>1.57</v>
+      </c>
+      <c r="K21" s="1">
+        <v>18.48</v>
+      </c>
+      <c r="L21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F22">
-        <v>11.77</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.44</v>
+        <v>11.03</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
       </c>
       <c r="H22">
-        <v>16.95</v>
+        <v>0.68</v>
       </c>
       <c r="I22" s="1">
-        <v>1.57</v>
+        <v>7.5</v>
       </c>
       <c r="J22">
-        <v>18.48</v>
-      </c>
-      <c r="K22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>0.68</v>
+      </c>
+      <c r="K22" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="L22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23">
+        <v>48.34</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23">
+        <v>1.51</v>
+      </c>
+      <c r="I23" s="1">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="J23">
+        <v>1.62</v>
+      </c>
+      <c r="K23" s="1">
+        <v>78.31</v>
+      </c>
+      <c r="L23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24">
         <v>3</v>
       </c>
-      <c r="D23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23">
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24">
         <v>36.27</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24">
         <v>0.67</v>
       </c>
-      <c r="H23">
+      <c r="I24" s="1">
         <v>24.3</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J24">
         <v>0.67</v>
       </c>
-      <c r="J23">
+      <c r="K24" s="1">
         <v>24.3</v>
       </c>
-      <c r="K23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24">
-        <v>48.34</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="H24">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="J24">
-        <v>78.31</v>
-      </c>
-      <c r="K24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F25">
         <v>19.36</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25">
         <v>1.42</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="1">
         <v>27.49</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>1.55</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>30.01</v>
       </c>
-      <c r="K25" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F26">
         <v>41.03</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26">
         <v>1.5</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="1">
         <v>61.54</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26">
         <v>1.56</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="1">
         <v>64.01000000000001</v>
       </c>
-      <c r="K26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F27">
         <v>34.94</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27">
         <v>1.42</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="1">
         <v>49.61</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>1.54</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>53.81</v>
       </c>
-      <c r="K27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F28">
         <v>19.45</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28">
         <v>0.66</v>
       </c>
-      <c r="H28">
+      <c r="I28" s="1">
         <v>12.84</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28">
         <v>0.66</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="1">
         <v>12.84</v>
       </c>
-      <c r="K28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F29">
         <v>18.68</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29">
         <v>1.47</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="1">
         <v>27.46</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29">
         <v>1.54</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="1">
         <v>28.77</v>
       </c>
-      <c r="K29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" t="s">
+        <v>101</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F30">
         <v>43.57</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30">
         <v>1.44</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="1">
         <v>62.74</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30">
         <v>1.52</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="1">
         <v>66.23</v>
       </c>
-      <c r="K30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>102</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F31">
+        <v>43.35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31">
+        <v>1.43</v>
+      </c>
+      <c r="I31" s="1">
+        <v>61.99</v>
+      </c>
+      <c r="J31">
+        <v>1.54</v>
+      </c>
+      <c r="K31" s="1">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="L31" t="s">
+        <v>103</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32">
+        <v>1.38</v>
+      </c>
+      <c r="I32" s="1">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="J32">
+        <v>1.51</v>
+      </c>
+      <c r="K32" s="1">
+        <v>109.41</v>
+      </c>
+      <c r="L32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33">
         <v>47.89</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G33" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33">
         <v>1.38</v>
       </c>
-      <c r="H31">
+      <c r="I33" s="1">
         <v>66.09</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J33">
         <v>1.51</v>
       </c>
-      <c r="J31">
+      <c r="K33" s="1">
         <v>72.31</v>
       </c>
-      <c r="K31" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="L33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34">
+        <v>21.83</v>
+      </c>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34">
+        <v>0.66</v>
+      </c>
+      <c r="I34" s="1">
+        <v>14.41</v>
+      </c>
+      <c r="J34">
+        <v>0.66</v>
+      </c>
+      <c r="K34" s="1">
+        <v>14.41</v>
+      </c>
+      <c r="L34" t="s">
+        <v>106</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35">
+        <v>36.9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35">
+        <v>1.37</v>
+      </c>
+      <c r="I35" s="1">
+        <v>50.55</v>
+      </c>
+      <c r="J35">
+        <v>1.5</v>
+      </c>
+      <c r="K35" s="1">
+        <v>55.35</v>
+      </c>
+      <c r="L35" t="s">
+        <v>107</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36">
+        <v>54.91</v>
+      </c>
+      <c r="G36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36">
+        <v>1.37</v>
+      </c>
+      <c r="I36" s="1">
+        <v>75.23</v>
+      </c>
+      <c r="J36">
+        <v>1.5</v>
+      </c>
+      <c r="K36" s="1">
+        <v>82.36</v>
+      </c>
+      <c r="L36" t="s">
+        <v>108</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37">
+        <v>37.67</v>
+      </c>
+      <c r="G37" t="s">
+        <v>74</v>
+      </c>
+      <c r="H37">
+        <v>1.4</v>
+      </c>
+      <c r="I37" s="1">
+        <v>52.74</v>
+      </c>
+      <c r="J37">
+        <v>1.51</v>
+      </c>
+      <c r="K37" s="1">
+        <v>56.88</v>
+      </c>
+      <c r="L37" t="s">
+        <v>109</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
         <v>46</v>
       </c>
-      <c r="C32">
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38">
+        <v>49.65</v>
+      </c>
+      <c r="G38" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38">
+        <v>1.4</v>
+      </c>
+      <c r="I38" s="1">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="J38">
+        <v>1.51</v>
+      </c>
+      <c r="K38" s="1">
+        <v>74.97</v>
+      </c>
+      <c r="L38" t="s">
+        <v>110</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39">
+        <v>43.43</v>
+      </c>
+      <c r="G39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39">
+        <v>1.4</v>
+      </c>
+      <c r="I39" s="1">
+        <v>60.8</v>
+      </c>
+      <c r="J39">
+        <v>1.51</v>
+      </c>
+      <c r="K39" s="1">
+        <v>65.58</v>
+      </c>
+      <c r="L39" t="s">
+        <v>111</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="6">
+        <v>934.8</v>
+      </c>
+      <c r="C44" s="6">
+        <v>22</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1.4978</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1400.14</v>
+      </c>
+      <c r="F44" s="6">
+        <v>1509.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="6">
+        <v>338.51</v>
+      </c>
+      <c r="C45" s="6">
         <v>9</v>
       </c>
-      <c r="D32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32">
-        <v>43.35</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H32">
-        <v>61.99</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J32">
-        <v>66.76000000000001</v>
-      </c>
-      <c r="K32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33">
-        <v>72.45999999999999</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1.38</v>
-      </c>
-      <c r="H33">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J33">
-        <v>109.41</v>
-      </c>
-      <c r="K33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="D45" s="7">
+        <v>1.3965</v>
+      </c>
+      <c r="E45" s="6">
+        <v>472.72</v>
+      </c>
+      <c r="F45" s="6">
+        <v>515.76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="6">
+        <v>160.04</v>
+      </c>
+      <c r="C46" s="6">
         <v>7</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="6">
-        <v>804.05</v>
-      </c>
-      <c r="C38" s="6">
-        <v>19</v>
-      </c>
-      <c r="D38" s="7">
-        <v>1.5137</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1217.09</v>
-      </c>
-      <c r="F38" s="6">
-        <v>1311.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="6">
-        <v>246.7</v>
-      </c>
-      <c r="C39" s="6">
-        <v>7</v>
-      </c>
-      <c r="D39" s="7">
-        <v>1.4063</v>
-      </c>
-      <c r="E39" s="6">
-        <v>346.94</v>
-      </c>
-      <c r="F39" s="6">
-        <v>378.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="6">
-        <v>138.21</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.6929</v>
-      </c>
-      <c r="E40" s="6">
-        <v>95.77</v>
-      </c>
-      <c r="F40" s="6">
-        <v>95.77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="9">
-        <v>1188.96</v>
-      </c>
-      <c r="C41" s="9">
-        <v>32</v>
-      </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="9">
-        <v>1659.8</v>
-      </c>
-      <c r="F41" s="9">
-        <v>1785.68</v>
+      <c r="D46" s="7">
+        <v>0.6885</v>
+      </c>
+      <c r="E46" s="6">
+        <v>110.18</v>
+      </c>
+      <c r="F46" s="6">
+        <v>110.18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1433.35</v>
+      </c>
+      <c r="C47" s="9">
+        <v>38</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="9">
+        <v>1983.04</v>
+      </c>
+      <c r="F47" s="9">
+        <v>2135.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -520,7 +520,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3127,7 +3127,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="7">
-        <v>1.4807</v>
+        <v>1.480665</v>
       </c>
       <c r="E54" s="6">
         <v>1643.76</v>
@@ -3147,7 +3147,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="7">
-        <v>1.3712</v>
+        <v>1.371249</v>
       </c>
       <c r="E55" s="6">
         <v>596.74</v>
@@ -3167,7 +3167,7 @@
         <v>4</v>
       </c>
       <c r="D56" s="7">
-        <v>1.6346</v>
+        <v>1.634552</v>
       </c>
       <c r="E56" s="6">
         <v>336.26</v>
@@ -3187,7 +3187,7 @@
         <v>4</v>
       </c>
       <c r="D57" s="7">
-        <v>0.6399</v>
+        <v>0.6399049999999999</v>
       </c>
       <c r="E57" s="6">
         <v>51.09</v>
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="7">
-        <v>1.2701</v>
+        <v>1.270115</v>
       </c>
       <c r="E58" s="6">
         <v>13.26</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="167">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -911,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -924,13 +927,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -973,2122 +976,2269 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2">
-        <v>38.29</v>
+        <v>38.292</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>53.61</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>53.570508</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.54</v>
       </c>
-      <c r="K2" s="1">
-        <v>58.97</v>
-      </c>
-      <c r="L2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>58.96968</v>
+      </c>
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3">
-        <v>63.28</v>
+        <v>63.279</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>88.59</v>
+        <v>1.399</v>
       </c>
       <c r="J3">
+        <v>88.527321</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.54</v>
       </c>
-      <c r="K3" s="1">
-        <v>97.45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="L3" s="1">
+        <v>97.44965999999999</v>
+      </c>
+      <c r="M3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4">
-        <v>23.91</v>
+        <v>23.906</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>0.64</v>
       </c>
       <c r="I4" s="1">
-        <v>15.3</v>
+        <v>0.64</v>
       </c>
       <c r="J4">
+        <v>15.29984</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="L4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="L4" s="1">
+        <v>15.29984</v>
+      </c>
+      <c r="M4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5">
-        <v>50.58</v>
+        <v>50.579</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I5" s="1">
-        <v>71.31999999999999</v>
+        <v>1.406</v>
       </c>
       <c r="J5">
+        <v>71.114074</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.52</v>
       </c>
-      <c r="K5" s="1">
-        <v>76.88</v>
-      </c>
-      <c r="L5" t="s">
-        <v>80</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="L5" s="1">
+        <v>76.88008000000001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>56.51</v>
+        <v>56.513</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I6" s="1">
-        <v>79.68000000000001</v>
+        <v>1.406</v>
       </c>
       <c r="J6">
+        <v>79.457278</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.52</v>
       </c>
-      <c r="K6" s="1">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="L6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="L6" s="1">
+        <v>85.89976</v>
+      </c>
+      <c r="M6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7">
-        <v>55.33</v>
+        <v>55.333</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I7" s="1">
-        <v>75.25</v>
+        <v>1.359</v>
       </c>
       <c r="J7">
+        <v>75.197547</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.5</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
+        <v>82.9995</v>
+      </c>
+      <c r="M7" t="s">
         <v>83</v>
       </c>
-      <c r="L7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8">
-        <v>41.72</v>
+        <v>41.719</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I8" s="1">
-        <v>58.83</v>
+        <v>1.406</v>
       </c>
       <c r="J8">
+        <v>58.656914</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.53</v>
       </c>
-      <c r="K8" s="1">
-        <v>63.83</v>
-      </c>
-      <c r="L8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>63.83007</v>
+      </c>
+      <c r="M8" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9">
-        <v>45.86</v>
+        <v>45.862</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I9" s="1">
-        <v>64.66</v>
+        <v>1.406</v>
       </c>
       <c r="J9">
+        <v>64.481972</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.52</v>
       </c>
-      <c r="K9" s="1">
-        <v>69.70999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="L9" s="1">
+        <v>69.71024</v>
+      </c>
+      <c r="M9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I10" s="1">
-        <v>93.06</v>
+        <v>1.406</v>
       </c>
       <c r="J10">
+        <v>92.79600000000001</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.56</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>102.96</v>
       </c>
-      <c r="L10" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="M10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11">
-        <v>58.25</v>
+        <v>58.253</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I11" s="1">
-        <v>79.22</v>
+        <v>1.359</v>
       </c>
       <c r="J11">
+        <v>79.16582699999999</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.5</v>
       </c>
-      <c r="K11" s="1">
-        <v>87.38</v>
-      </c>
-      <c r="L11" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="L11" s="1">
+        <v>87.37949999999999</v>
+      </c>
+      <c r="M11" t="s">
+        <v>87</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>4.99</v>
       </c>
       <c r="I12" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="J12">
         <v>9.98</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>4.99</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>9.98</v>
       </c>
-      <c r="L12" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13">
-        <v>26.05</v>
+        <v>26.053</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I13" s="1">
-        <v>35.43</v>
+        <v>1.359</v>
       </c>
       <c r="J13">
+        <v>35.406027</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.52</v>
       </c>
-      <c r="K13" s="1">
-        <v>39.6</v>
-      </c>
-      <c r="L13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>39.60056</v>
+      </c>
+      <c r="M13" t="s">
+        <v>88</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14">
-        <v>28.59</v>
+        <v>28.587</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I14" s="1">
-        <v>40.31</v>
+        <v>1.412</v>
       </c>
       <c r="J14">
+        <v>40.364844</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.55</v>
       </c>
-      <c r="K14" s="1">
-        <v>44.31</v>
-      </c>
-      <c r="L14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="1">
+        <v>44.30985</v>
+      </c>
+      <c r="M14" t="s">
+        <v>89</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15">
-        <v>41.29</v>
+        <v>41.289</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I15" s="1">
-        <v>58.22</v>
+        <v>1.412</v>
       </c>
       <c r="J15">
+        <v>58.300068</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.52</v>
       </c>
-      <c r="K15" s="1">
-        <v>62.76</v>
-      </c>
-      <c r="L15" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="1">
+        <v>62.75928</v>
+      </c>
+      <c r="M15" t="s">
+        <v>90</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16">
         <v>66.8</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16">
-        <v>1.63</v>
+        <v>1.629</v>
       </c>
       <c r="I16" s="1">
-        <v>108.88</v>
+        <v>1.629</v>
       </c>
       <c r="J16">
+        <v>108.8172</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.75</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>116.9</v>
       </c>
-      <c r="L16" t="s">
-        <v>90</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="M16" t="s">
+        <v>91</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>42.78</v>
+        <v>42.783</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I17" s="1">
-        <v>60.32</v>
+        <v>1.412</v>
       </c>
       <c r="J17">
+        <v>60.409596</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.52</v>
       </c>
-      <c r="K17" s="1">
-        <v>65.03</v>
-      </c>
-      <c r="L17" t="s">
-        <v>91</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="1">
+        <v>65.03016</v>
+      </c>
+      <c r="M17" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18">
-        <v>63.49</v>
+        <v>63.487</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I18" s="1">
-        <v>86.34999999999999</v>
+        <v>1.359</v>
       </c>
       <c r="J18">
+        <v>86.27883300000001</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.52</v>
       </c>
-      <c r="K18" s="1">
-        <v>96.5</v>
-      </c>
-      <c r="L18" t="s">
-        <v>92</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="1">
+        <v>96.50024000000001</v>
+      </c>
+      <c r="M18" t="s">
+        <v>93</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19">
-        <v>55.13</v>
+        <v>55.134</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19">
-        <v>1.44</v>
+        <v>1.437</v>
       </c>
       <c r="I19" s="1">
-        <v>79.39</v>
+        <v>1.437</v>
       </c>
       <c r="J19">
+        <v>79.227558</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.57</v>
       </c>
-      <c r="K19" s="1">
-        <v>86.55</v>
-      </c>
-      <c r="L19" t="s">
-        <v>93</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="L19" s="1">
+        <v>86.56037999999999</v>
+      </c>
+      <c r="M19" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20">
         <v>4.99</v>
       </c>
       <c r="I20" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="J20">
         <v>14.97</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>4.99</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>14.97</v>
       </c>
-      <c r="L20" t="s">
-        <v>93</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="M20" t="s">
+        <v>94</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21">
-        <v>36.73</v>
+        <v>36.729</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21">
-        <v>1.63</v>
+        <v>1.629</v>
       </c>
       <c r="I21" s="1">
-        <v>59.87</v>
+        <v>1.629</v>
       </c>
       <c r="J21">
+        <v>59.831541</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.77</v>
       </c>
-      <c r="K21" s="1">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="L21" t="s">
-        <v>94</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="L21" s="1">
+        <v>65.01033</v>
+      </c>
+      <c r="M21" t="s">
+        <v>95</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22">
-        <v>46.56</v>
+        <v>46.557</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I22" s="1">
-        <v>63.32</v>
+        <v>1.359</v>
       </c>
       <c r="J22">
+        <v>63.270963</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.49</v>
       </c>
-      <c r="K22" s="1">
-        <v>69.37</v>
-      </c>
-      <c r="L22" t="s">
-        <v>95</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="1">
+        <v>69.36993</v>
+      </c>
+      <c r="M22" t="s">
+        <v>96</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23">
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23">
-        <v>54.42</v>
+        <v>54.418</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23">
-        <v>1.44</v>
+        <v>1.437</v>
       </c>
       <c r="I23" s="1">
-        <v>78.36</v>
+        <v>1.437</v>
       </c>
       <c r="J23">
+        <v>78.198666</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.58</v>
       </c>
-      <c r="K23" s="1">
-        <v>85.98</v>
-      </c>
-      <c r="L23" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="L23" s="1">
+        <v>85.98044</v>
+      </c>
+      <c r="M23" t="s">
+        <v>97</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F24">
-        <v>10.44</v>
+        <v>10.441</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24">
         <v>1.27</v>
       </c>
       <c r="I24" s="1">
-        <v>13.26</v>
+        <v>1.27</v>
       </c>
       <c r="J24">
+        <v>13.26007</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.27</v>
       </c>
-      <c r="K24" s="1">
-        <v>13.26</v>
-      </c>
-      <c r="L24" t="s">
-        <v>96</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="L24" s="1">
+        <v>13.26007</v>
+      </c>
+      <c r="M24" t="s">
+        <v>97</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25">
-        <v>55.41</v>
+        <v>55.409</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25">
-        <v>1.63</v>
+        <v>1.629</v>
       </c>
       <c r="I25" s="1">
-        <v>90.31999999999999</v>
+        <v>1.629</v>
       </c>
       <c r="J25">
+        <v>90.261261</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.76</v>
       </c>
-      <c r="K25" s="1">
-        <v>97.52</v>
-      </c>
-      <c r="L25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="L25" s="1">
+        <v>97.51984</v>
+      </c>
+      <c r="M25" t="s">
+        <v>98</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F26">
-        <v>54.87</v>
+        <v>54.873</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26">
-        <v>1.36</v>
+        <v>1.359</v>
       </c>
       <c r="I26" s="1">
-        <v>74.62</v>
+        <v>1.359</v>
       </c>
       <c r="J26">
+        <v>74.572407</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.5</v>
       </c>
-      <c r="K26" s="1">
-        <v>82.3</v>
-      </c>
-      <c r="L26" t="s">
-        <v>98</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="L26" s="1">
+        <v>82.3095</v>
+      </c>
+      <c r="M26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27">
-        <v>49.01</v>
+        <v>49.013</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27">
-        <v>1.49</v>
+        <v>1.489</v>
       </c>
       <c r="I27" s="1">
-        <v>73.02</v>
+        <v>1.489</v>
       </c>
       <c r="J27">
+        <v>72.980357</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.58</v>
       </c>
-      <c r="K27" s="1">
-        <v>77.44</v>
-      </c>
-      <c r="L27" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="L27" s="1">
+        <v>77.44054</v>
+      </c>
+      <c r="M27" t="s">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F28">
-        <v>24.73</v>
+        <v>24.733</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H28">
-        <v>1.37</v>
+        <v>1.369</v>
       </c>
       <c r="I28" s="1">
-        <v>33.88</v>
+        <v>1.369</v>
       </c>
       <c r="J28">
+        <v>33.859477</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.5</v>
       </c>
-      <c r="K28" s="1">
-        <v>37.1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="L28" s="1">
+        <v>37.0995</v>
+      </c>
+      <c r="M28" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29">
         <v>4.99</v>
       </c>
       <c r="I29" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="J29">
         <v>14.97</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="1">
         <v>4.99</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>14.97</v>
       </c>
-      <c r="L29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="M29" t="s">
+        <v>101</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30">
-        <v>48.76</v>
+        <v>48.758</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H30">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="I30" s="1">
-        <v>73.14</v>
+        <v>1.499</v>
       </c>
       <c r="J30">
+        <v>73.08824199999999</v>
+      </c>
+      <c r="K30" s="1">
         <v>1.61</v>
       </c>
-      <c r="K30" s="1">
-        <v>78.5</v>
-      </c>
-      <c r="L30" t="s">
-        <v>101</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="L30" s="1">
+        <v>78.50038000000001</v>
+      </c>
+      <c r="M30" t="s">
+        <v>102</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F31">
-        <v>33.73</v>
+        <v>33.733</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H31">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="I31" s="1">
-        <v>50.6</v>
+        <v>1.499</v>
       </c>
       <c r="J31">
+        <v>50.565767</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.61</v>
       </c>
-      <c r="K31" s="1">
-        <v>54.31</v>
-      </c>
-      <c r="L31" t="s">
-        <v>102</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="L31" s="1">
+        <v>54.31013</v>
+      </c>
+      <c r="M31" t="s">
+        <v>103</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F32">
-        <v>21.98</v>
+        <v>21.982</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H32">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="I32" s="1">
-        <v>32.97</v>
+        <v>1.499</v>
       </c>
       <c r="J32">
+        <v>32.951018</v>
+      </c>
+      <c r="K32" s="1">
         <v>1.63</v>
       </c>
-      <c r="K32" s="1">
-        <v>35.83</v>
-      </c>
-      <c r="L32" t="s">
-        <v>103</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="L32" s="1">
+        <v>35.83066</v>
+      </c>
+      <c r="M32" t="s">
+        <v>104</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F33">
-        <v>40.5</v>
+        <v>40.503</v>
       </c>
       <c r="G33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H33">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="I33" s="1">
-        <v>60.75</v>
+        <v>1.499</v>
       </c>
       <c r="J33">
+        <v>60.713997</v>
+      </c>
+      <c r="K33" s="1">
         <v>1.63</v>
       </c>
-      <c r="K33" s="1">
-        <v>66.02</v>
-      </c>
-      <c r="L33" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="L33" s="1">
+        <v>66.01989</v>
+      </c>
+      <c r="M33" t="s">
+        <v>105</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F34">
-        <v>34.49</v>
+        <v>34.487</v>
       </c>
       <c r="G34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H34">
-        <v>1.37</v>
+        <v>1.369</v>
       </c>
       <c r="I34" s="1">
-        <v>47.25</v>
+        <v>1.369</v>
       </c>
       <c r="J34">
+        <v>47.212703</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.52</v>
       </c>
-      <c r="K34" s="1">
-        <v>52.42</v>
-      </c>
-      <c r="L34" t="s">
-        <v>105</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="L34" s="1">
+        <v>52.42024</v>
+      </c>
+      <c r="M34" t="s">
+        <v>106</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35">
         <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H35">
-        <v>1.53</v>
+        <v>1.528</v>
       </c>
       <c r="I35" s="1">
-        <v>87.20999999999999</v>
+        <v>1.528</v>
       </c>
       <c r="J35">
+        <v>87.096</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.68</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>95.76000000000001</v>
       </c>
-      <c r="L35" t="s">
-        <v>106</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="M35" t="s">
+        <v>107</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F36">
         <v>40.69</v>
       </c>
       <c r="G36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H36">
-        <v>1.56</v>
+        <v>1.564</v>
       </c>
       <c r="I36" s="1">
-        <v>63.48</v>
+        <v>1.564</v>
       </c>
       <c r="J36">
+        <v>63.63916</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.68</v>
       </c>
-      <c r="K36" s="1">
-        <v>68.36</v>
-      </c>
-      <c r="L36" t="s">
-        <v>107</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="L36" s="1">
+        <v>68.3592</v>
+      </c>
+      <c r="M36" t="s">
+        <v>108</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37">
-        <v>41.41</v>
+        <v>41.411</v>
       </c>
       <c r="G37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H37">
-        <v>1.56</v>
+        <v>1.564</v>
       </c>
       <c r="I37" s="1">
-        <v>64.59999999999999</v>
+        <v>1.564</v>
       </c>
       <c r="J37">
+        <v>64.76680399999999</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.68</v>
       </c>
-      <c r="K37" s="1">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="L37" t="s">
-        <v>108</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="L37" s="1">
+        <v>69.57048</v>
+      </c>
+      <c r="M37" t="s">
+        <v>109</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F38">
-        <v>60.06</v>
+        <v>60.059</v>
       </c>
       <c r="G38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H38">
-        <v>1.59</v>
+        <v>1.588</v>
       </c>
       <c r="I38" s="1">
-        <v>95.5</v>
+        <v>1.588</v>
       </c>
       <c r="J38">
+        <v>95.37369200000001</v>
+      </c>
+      <c r="K38" s="1">
         <v>1.69</v>
       </c>
-      <c r="K38" s="1">
-        <v>101.5</v>
-      </c>
-      <c r="L38" t="s">
-        <v>109</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="L38" s="1">
+        <v>101.49971</v>
+      </c>
+      <c r="M38" t="s">
+        <v>110</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F39">
-        <v>8.84</v>
+        <v>8.840999999999999</v>
       </c>
       <c r="G39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H39">
-        <v>1.59</v>
+        <v>1.588</v>
       </c>
       <c r="I39" s="1">
-        <v>14.06</v>
+        <v>1.588</v>
       </c>
       <c r="J39">
+        <v>14.039508</v>
+      </c>
+      <c r="K39" s="1">
         <v>1.7</v>
       </c>
-      <c r="K39" s="1">
-        <v>15.03</v>
-      </c>
-      <c r="L39" t="s">
-        <v>110</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="L39" s="1">
+        <v>15.0297</v>
+      </c>
+      <c r="M39" t="s">
+        <v>111</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F40">
         <v>46.78</v>
       </c>
       <c r="G40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H40">
-        <v>1.65</v>
+        <v>1.649</v>
       </c>
       <c r="I40" s="1">
-        <v>77.19</v>
+        <v>1.649</v>
       </c>
       <c r="J40">
+        <v>77.14022</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.82</v>
       </c>
-      <c r="K40" s="1">
-        <v>85.14</v>
-      </c>
-      <c r="L40" t="s">
-        <v>111</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="L40" s="1">
+        <v>85.1396</v>
+      </c>
+      <c r="M40" t="s">
+        <v>112</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F41">
-        <v>18.56</v>
+        <v>18.558</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H41">
-        <v>1.4</v>
+        <v>1.401</v>
       </c>
       <c r="I41" s="1">
-        <v>25.98</v>
+        <v>1.401</v>
       </c>
       <c r="J41">
+        <v>25.999758</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.56</v>
       </c>
-      <c r="K41" s="1">
-        <v>28.95</v>
-      </c>
-      <c r="L41" t="s">
-        <v>112</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="L41" s="1">
+        <v>28.95048</v>
+      </c>
+      <c r="M41" t="s">
+        <v>113</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F42">
-        <v>12.86</v>
+        <v>12.859</v>
       </c>
       <c r="G42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H42">
         <v>0.64</v>
       </c>
       <c r="I42" s="1">
-        <v>8.23</v>
+        <v>0.64</v>
       </c>
       <c r="J42">
+        <v>8.229760000000001</v>
+      </c>
+      <c r="K42" s="1">
         <v>0.64</v>
       </c>
-      <c r="K42" s="1">
-        <v>8.23</v>
-      </c>
-      <c r="L42" t="s">
-        <v>112</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="L42" s="1">
+        <v>8.229760000000001</v>
+      </c>
+      <c r="M42" t="s">
+        <v>113</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43">
-        <v>22.87</v>
+        <v>22.869</v>
       </c>
       <c r="G43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H43">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="I43" s="1">
-        <v>37.05</v>
+        <v>1.619</v>
       </c>
       <c r="J43">
+        <v>37.024911</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.75</v>
       </c>
-      <c r="K43" s="1">
-        <v>40.02</v>
-      </c>
-      <c r="L43" t="s">
-        <v>113</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="L43" s="1">
+        <v>40.02075</v>
+      </c>
+      <c r="M43" t="s">
+        <v>114</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F44">
-        <v>23.9</v>
+        <v>23.899</v>
       </c>
       <c r="G44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H44">
-        <v>1.4</v>
+        <v>1.401</v>
       </c>
       <c r="I44" s="1">
-        <v>33.46</v>
+        <v>1.401</v>
       </c>
       <c r="J44">
+        <v>33.482499</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.59</v>
       </c>
-      <c r="K44" s="1">
-        <v>38</v>
-      </c>
-      <c r="L44" t="s">
-        <v>77</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="L44" s="1">
+        <v>37.99941</v>
+      </c>
+      <c r="M44" t="s">
+        <v>78</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F45">
-        <v>45.73</v>
+        <v>45.731</v>
       </c>
       <c r="G45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H45">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="I45" s="1">
-        <v>74.08</v>
+        <v>1.619</v>
       </c>
       <c r="J45">
+        <v>74.038489</v>
+      </c>
+      <c r="K45" s="1">
         <v>1.75</v>
       </c>
-      <c r="K45" s="1">
-        <v>80.03</v>
-      </c>
-      <c r="L45" t="s">
-        <v>114</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="L45" s="1">
+        <v>80.02925</v>
+      </c>
+      <c r="M45" t="s">
+        <v>115</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F46">
         <v>55.12</v>
       </c>
       <c r="G46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H46">
-        <v>1.65</v>
+        <v>1.653</v>
       </c>
       <c r="I46" s="1">
-        <v>90.95</v>
+        <v>1.653</v>
       </c>
       <c r="J46">
+        <v>91.11336</v>
+      </c>
+      <c r="K46" s="1">
         <v>1.75</v>
       </c>
-      <c r="K46" s="1">
+      <c r="L46" s="1">
         <v>96.45999999999999</v>
       </c>
-      <c r="L46" t="s">
-        <v>115</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="M46" t="s">
+        <v>116</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C47">
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F47">
-        <v>28.95</v>
+        <v>28.955</v>
       </c>
       <c r="G47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H47">
-        <v>1.45</v>
+        <v>1.449</v>
       </c>
       <c r="I47" s="1">
-        <v>41.98</v>
+        <v>1.449</v>
       </c>
       <c r="J47">
+        <v>41.955795</v>
+      </c>
+      <c r="K47" s="1">
         <v>1.55</v>
       </c>
-      <c r="K47" s="1">
-        <v>44.87</v>
-      </c>
-      <c r="L47" t="s">
-        <v>116</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="L47" s="1">
+        <v>44.88025</v>
+      </c>
+      <c r="M47" t="s">
+        <v>117</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F48">
-        <v>20.55</v>
+        <v>20.547</v>
       </c>
       <c r="G48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H48">
         <v>0.64</v>
       </c>
       <c r="I48" s="1">
-        <v>13.15</v>
+        <v>0.64</v>
       </c>
       <c r="J48">
+        <v>13.15008</v>
+      </c>
+      <c r="K48" s="1">
         <v>0.64</v>
       </c>
-      <c r="K48" s="1">
-        <v>13.15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>116</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="L48" s="1">
+        <v>13.15008</v>
+      </c>
+      <c r="M48" t="s">
+        <v>117</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F49">
-        <v>22.52</v>
+        <v>22.516</v>
       </c>
       <c r="G49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49">
         <v>0.64</v>
       </c>
       <c r="I49" s="1">
-        <v>14.41</v>
+        <v>0.64</v>
       </c>
       <c r="J49">
+        <v>14.41024</v>
+      </c>
+      <c r="K49" s="1">
         <v>0.64</v>
       </c>
-      <c r="K49" s="1">
-        <v>14.41</v>
-      </c>
-      <c r="L49" t="s">
-        <v>117</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="L49" s="1">
+        <v>14.41024</v>
+      </c>
+      <c r="M49" t="s">
+        <v>118</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3096,98 +3246,98 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:15">
       <c r="A53" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B54" s="6">
-        <v>1110.15</v>
+        <v>1110.165</v>
       </c>
       <c r="C54" s="6">
         <v>25</v>
       </c>
       <c r="D54" s="7">
-        <v>1.480665</v>
+        <v>1.479506</v>
       </c>
       <c r="E54" s="6">
-        <v>1643.76</v>
+        <v>1642.5</v>
       </c>
       <c r="F54" s="6">
-        <v>1779.16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+        <v>1779.17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B55" s="6">
-        <v>435.18</v>
+        <v>435.188</v>
       </c>
       <c r="C55" s="6">
         <v>11</v>
       </c>
       <c r="D55" s="7">
-        <v>1.371249</v>
+        <v>1.370446</v>
       </c>
       <c r="E55" s="6">
-        <v>596.74</v>
+        <v>596.4</v>
       </c>
       <c r="F55" s="6">
-        <v>659.49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+        <v>659.51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B56" s="6">
-        <v>205.72</v>
+        <v>205.718</v>
       </c>
       <c r="C56" s="6">
         <v>4</v>
       </c>
       <c r="D56" s="7">
-        <v>1.634552</v>
+        <v>1.633548</v>
       </c>
       <c r="E56" s="6">
-        <v>336.26</v>
+        <v>336.05</v>
       </c>
       <c r="F56" s="6">
         <v>364.57</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:15">
       <c r="A57" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B57" s="6">
-        <v>79.84</v>
+        <v>79.828</v>
       </c>
       <c r="C57" s="6">
         <v>4</v>
       </c>
       <c r="D57" s="7">
-        <v>0.6399049999999999</v>
+        <v>0.64</v>
       </c>
       <c r="E57" s="6">
         <v>51.09</v>
@@ -3196,18 +3346,18 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:15">
       <c r="A58" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B58" s="6">
-        <v>10.44</v>
+        <v>10.441</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
       </c>
       <c r="D58" s="7">
-        <v>1.270115</v>
+        <v>1.27</v>
       </c>
       <c r="E58" s="6">
         <v>13.26</v>
@@ -3216,9 +3366,9 @@
         <v>13.26</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:15">
       <c r="A59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B59" s="6">
         <v>8</v>
@@ -3236,22 +3386,22 @@
         <v>39.92</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:15">
       <c r="A60" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B60" s="9">
-        <v>1849.33</v>
+        <v>1849.34</v>
       </c>
       <c r="C60" s="9">
         <v>48</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="9">
-        <v>2681.03</v>
+        <v>2679.22</v>
       </c>
       <c r="F60" s="9">
-        <v>2907.49</v>
+        <v>2907.52</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="166">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -522,8 +519,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -616,10 +613,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -927,13 +924,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -976,2269 +973,2122 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2">
         <v>38.292</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>1.399</v>
+        <v>53.571</v>
       </c>
       <c r="J2">
-        <v>53.570508</v>
+        <v>1.54</v>
       </c>
       <c r="K2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L2" s="1">
-        <v>58.96968</v>
-      </c>
-      <c r="M2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>58.97</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>63.279</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H3">
         <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>88.527</v>
       </c>
       <c r="J3">
-        <v>88.527321</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>97.44965999999999</v>
-      </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>97.45</v>
+      </c>
+      <c r="L3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>23.906</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>0.64</v>
       </c>
       <c r="I4" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="J4">
         <v>0.64</v>
       </c>
-      <c r="J4">
-        <v>15.29984</v>
-      </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>15.29984</v>
-      </c>
-      <c r="M4" t="s">
-        <v>80</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>15.3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>50.579</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5">
         <v>1.406</v>
       </c>
       <c r="I5" s="1">
-        <v>1.406</v>
+        <v>71.114</v>
       </c>
       <c r="J5">
-        <v>71.114074</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>76.88008000000001</v>
-      </c>
-      <c r="M5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>76.88</v>
+      </c>
+      <c r="L5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>56.513</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>1.406</v>
       </c>
       <c r="I6" s="1">
-        <v>1.406</v>
+        <v>79.45699999999999</v>
       </c>
       <c r="J6">
-        <v>79.457278</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
-        <v>85.89976</v>
-      </c>
-      <c r="M6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="L6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7">
         <v>55.333</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7">
         <v>1.359</v>
       </c>
       <c r="I7" s="1">
-        <v>1.359</v>
+        <v>75.19799999999999</v>
       </c>
       <c r="J7">
-        <v>75.197547</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="1">
-        <v>82.9995</v>
-      </c>
-      <c r="M7" t="s">
         <v>83</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>41.719</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8">
         <v>1.406</v>
       </c>
       <c r="I8" s="1">
-        <v>1.406</v>
+        <v>58.657</v>
       </c>
       <c r="J8">
-        <v>58.656914</v>
+        <v>1.53</v>
       </c>
       <c r="K8" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L8" s="1">
-        <v>63.83007</v>
-      </c>
-      <c r="M8" t="s">
-        <v>84</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>63.83</v>
+      </c>
+      <c r="L8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>45.862</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>1.406</v>
       </c>
       <c r="I9" s="1">
-        <v>1.406</v>
+        <v>64.482</v>
       </c>
       <c r="J9">
-        <v>64.481972</v>
+        <v>1.52</v>
       </c>
       <c r="K9" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L9" s="1">
-        <v>69.71024</v>
-      </c>
-      <c r="M9" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>1.406</v>
       </c>
       <c r="I10" s="1">
-        <v>1.406</v>
+        <v>92.79600000000001</v>
       </c>
       <c r="J10">
-        <v>92.79600000000001</v>
+        <v>1.56</v>
       </c>
       <c r="K10" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L10" s="1">
         <v>102.96</v>
       </c>
-      <c r="M10" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11">
         <v>58.253</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11">
         <v>1.359</v>
       </c>
       <c r="I11" s="1">
-        <v>1.359</v>
+        <v>79.166</v>
       </c>
       <c r="J11">
-        <v>79.16582699999999</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="1">
-        <v>87.37949999999999</v>
-      </c>
-      <c r="M11" t="s">
-        <v>87</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>87.38</v>
+      </c>
+      <c r="L11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>4.99</v>
       </c>
       <c r="I12" s="1">
+        <v>9.98</v>
+      </c>
+      <c r="J12">
         <v>4.99</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>9.98</v>
       </c>
-      <c r="K12" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="L12" s="1">
-        <v>9.98</v>
-      </c>
-      <c r="M12" t="s">
-        <v>87</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="L12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13">
         <v>26.053</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13">
         <v>1.359</v>
       </c>
       <c r="I13" s="1">
-        <v>1.359</v>
+        <v>35.406</v>
       </c>
       <c r="J13">
-        <v>35.406027</v>
+        <v>1.52</v>
       </c>
       <c r="K13" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L13" s="1">
-        <v>39.60056</v>
-      </c>
-      <c r="M13" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>39.601</v>
+      </c>
+      <c r="L13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <v>28.587</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14">
         <v>1.412</v>
       </c>
       <c r="I14" s="1">
-        <v>1.412</v>
+        <v>40.365</v>
       </c>
       <c r="J14">
-        <v>40.364844</v>
+        <v>1.55</v>
       </c>
       <c r="K14" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L14" s="1">
-        <v>44.30985</v>
-      </c>
-      <c r="M14" t="s">
-        <v>89</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>44.31</v>
+      </c>
+      <c r="L14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15">
         <v>41.289</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15">
         <v>1.412</v>
       </c>
       <c r="I15" s="1">
-        <v>1.412</v>
+        <v>58.3</v>
       </c>
       <c r="J15">
-        <v>58.300068</v>
+        <v>1.52</v>
       </c>
       <c r="K15" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L15" s="1">
-        <v>62.75928</v>
-      </c>
-      <c r="M15" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>62.759</v>
+      </c>
+      <c r="L15" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16">
         <v>66.8</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16">
         <v>1.629</v>
       </c>
       <c r="I16" s="1">
-        <v>1.629</v>
+        <v>108.817</v>
       </c>
       <c r="J16">
-        <v>108.8172</v>
+        <v>1.75</v>
       </c>
       <c r="K16" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L16" s="1">
         <v>116.9</v>
       </c>
-      <c r="M16" t="s">
-        <v>91</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17">
         <v>42.783</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H17">
         <v>1.412</v>
       </c>
       <c r="I17" s="1">
-        <v>1.412</v>
+        <v>60.41</v>
       </c>
       <c r="J17">
-        <v>60.409596</v>
+        <v>1.52</v>
       </c>
       <c r="K17" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L17" s="1">
-        <v>65.03016</v>
-      </c>
-      <c r="M17" t="s">
-        <v>92</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>65.03</v>
+      </c>
+      <c r="L17" t="s">
+        <v>91</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18">
         <v>63.487</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18">
         <v>1.359</v>
       </c>
       <c r="I18" s="1">
-        <v>1.359</v>
+        <v>86.279</v>
       </c>
       <c r="J18">
-        <v>86.27883300000001</v>
+        <v>1.52</v>
       </c>
       <c r="K18" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L18" s="1">
-        <v>96.50024000000001</v>
-      </c>
-      <c r="M18" t="s">
-        <v>93</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>96.5</v>
+      </c>
+      <c r="L18" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19">
         <v>55.134</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19">
         <v>1.437</v>
       </c>
       <c r="I19" s="1">
-        <v>1.437</v>
+        <v>79.22799999999999</v>
       </c>
       <c r="J19">
-        <v>79.227558</v>
+        <v>1.57</v>
       </c>
       <c r="K19" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="L19" s="1">
-        <v>86.56037999999999</v>
-      </c>
-      <c r="M19" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>86.56</v>
+      </c>
+      <c r="L19" t="s">
+        <v>93</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H20">
         <v>4.99</v>
       </c>
       <c r="I20" s="1">
+        <v>14.97</v>
+      </c>
+      <c r="J20">
         <v>4.99</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>14.97</v>
       </c>
-      <c r="K20" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="L20" s="1">
-        <v>14.97</v>
-      </c>
-      <c r="M20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21">
         <v>36.729</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21">
         <v>1.629</v>
       </c>
       <c r="I21" s="1">
-        <v>1.629</v>
+        <v>59.832</v>
       </c>
       <c r="J21">
-        <v>59.831541</v>
+        <v>1.77</v>
       </c>
       <c r="K21" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L21" s="1">
-        <v>65.01033</v>
-      </c>
-      <c r="M21" t="s">
-        <v>95</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="L21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22">
         <v>46.557</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22">
         <v>1.359</v>
       </c>
       <c r="I22" s="1">
-        <v>1.359</v>
+        <v>63.271</v>
       </c>
       <c r="J22">
-        <v>63.270963</v>
+        <v>1.49</v>
       </c>
       <c r="K22" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L22" s="1">
-        <v>69.36993</v>
-      </c>
-      <c r="M22" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>69.37</v>
+      </c>
+      <c r="L22" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23">
         <v>54.418</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23">
         <v>1.437</v>
       </c>
       <c r="I23" s="1">
-        <v>1.437</v>
+        <v>78.199</v>
       </c>
       <c r="J23">
-        <v>78.198666</v>
+        <v>1.58</v>
       </c>
       <c r="K23" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L23" s="1">
-        <v>85.98044</v>
-      </c>
-      <c r="M23" t="s">
-        <v>97</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>85.98</v>
+      </c>
+      <c r="L23" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24">
         <v>10.441</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24">
         <v>1.27</v>
       </c>
       <c r="I24" s="1">
+        <v>13.26</v>
+      </c>
+      <c r="J24">
         <v>1.27</v>
       </c>
-      <c r="J24">
-        <v>13.26007</v>
-      </c>
       <c r="K24" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="L24" s="1">
-        <v>13.26007</v>
-      </c>
-      <c r="M24" t="s">
-        <v>97</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>13.26</v>
+      </c>
+      <c r="L24" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25">
         <v>55.409</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25">
         <v>1.629</v>
       </c>
       <c r="I25" s="1">
-        <v>1.629</v>
+        <v>90.261</v>
       </c>
       <c r="J25">
-        <v>90.261261</v>
+        <v>1.76</v>
       </c>
       <c r="K25" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L25" s="1">
-        <v>97.51984</v>
-      </c>
-      <c r="M25" t="s">
-        <v>98</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>97.52</v>
+      </c>
+      <c r="L25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26">
         <v>54.873</v>
       </c>
       <c r="G26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26">
         <v>1.359</v>
       </c>
       <c r="I26" s="1">
-        <v>1.359</v>
+        <v>74.572</v>
       </c>
       <c r="J26">
-        <v>74.572407</v>
+        <v>1.5</v>
       </c>
       <c r="K26" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L26" s="1">
-        <v>82.3095</v>
-      </c>
-      <c r="M26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>82.31</v>
+      </c>
+      <c r="L26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27">
         <v>49.013</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27">
         <v>1.489</v>
       </c>
       <c r="I27" s="1">
-        <v>1.489</v>
+        <v>72.98</v>
       </c>
       <c r="J27">
-        <v>72.980357</v>
+        <v>1.58</v>
       </c>
       <c r="K27" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L27" s="1">
-        <v>77.44054</v>
-      </c>
-      <c r="M27" t="s">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>77.441</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28">
         <v>24.733</v>
       </c>
       <c r="G28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H28">
         <v>1.369</v>
       </c>
       <c r="I28" s="1">
-        <v>1.369</v>
+        <v>33.859</v>
       </c>
       <c r="J28">
-        <v>33.859477</v>
+        <v>1.5</v>
       </c>
       <c r="K28" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L28" s="1">
-        <v>37.0995</v>
-      </c>
-      <c r="M28" t="s">
-        <v>101</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>37.1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H29">
         <v>4.99</v>
       </c>
       <c r="I29" s="1">
+        <v>14.97</v>
+      </c>
+      <c r="J29">
         <v>4.99</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="1">
         <v>14.97</v>
       </c>
-      <c r="K29" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="L29" s="1">
-        <v>14.97</v>
-      </c>
-      <c r="M29" t="s">
-        <v>101</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="L29" t="s">
+        <v>100</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>19</v>
       </c>
       <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
         <v>69</v>
-      </c>
-      <c r="E30" t="s">
-        <v>70</v>
       </c>
       <c r="F30">
         <v>48.758</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30">
         <v>1.499</v>
       </c>
       <c r="I30" s="1">
-        <v>1.499</v>
+        <v>73.08799999999999</v>
       </c>
       <c r="J30">
-        <v>73.08824199999999</v>
+        <v>1.61</v>
       </c>
       <c r="K30" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L30" s="1">
-        <v>78.50038000000001</v>
-      </c>
-      <c r="M30" t="s">
-        <v>102</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>78.5</v>
+      </c>
+      <c r="L30" t="s">
+        <v>101</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F31">
         <v>33.733</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H31">
         <v>1.499</v>
       </c>
       <c r="I31" s="1">
-        <v>1.499</v>
+        <v>50.566</v>
       </c>
       <c r="J31">
-        <v>50.565767</v>
+        <v>1.61</v>
       </c>
       <c r="K31" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L31" s="1">
-        <v>54.31013</v>
-      </c>
-      <c r="M31" t="s">
-        <v>103</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>54.31</v>
+      </c>
+      <c r="L31" t="s">
+        <v>102</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32">
         <v>21.982</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H32">
         <v>1.499</v>
       </c>
       <c r="I32" s="1">
-        <v>1.499</v>
+        <v>32.951</v>
       </c>
       <c r="J32">
-        <v>32.951018</v>
+        <v>1.63</v>
       </c>
       <c r="K32" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L32" s="1">
-        <v>35.83066</v>
-      </c>
-      <c r="M32" t="s">
-        <v>104</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>35.831</v>
+      </c>
+      <c r="L32" t="s">
+        <v>103</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33">
         <v>40.503</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H33">
         <v>1.499</v>
       </c>
       <c r="I33" s="1">
-        <v>1.499</v>
+        <v>60.714</v>
       </c>
       <c r="J33">
-        <v>60.713997</v>
+        <v>1.63</v>
       </c>
       <c r="K33" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L33" s="1">
-        <v>66.01989</v>
-      </c>
-      <c r="M33" t="s">
-        <v>105</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>66.02</v>
+      </c>
+      <c r="L33" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34">
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F34">
         <v>34.487</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H34">
         <v>1.369</v>
       </c>
       <c r="I34" s="1">
-        <v>1.369</v>
+        <v>47.213</v>
       </c>
       <c r="J34">
-        <v>47.212703</v>
+        <v>1.52</v>
       </c>
       <c r="K34" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L34" s="1">
-        <v>52.42024</v>
-      </c>
-      <c r="M34" t="s">
-        <v>106</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>52.42</v>
+      </c>
+      <c r="L34" t="s">
+        <v>105</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35">
         <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H35">
         <v>1.528</v>
       </c>
       <c r="I35" s="1">
-        <v>1.528</v>
+        <v>87.096</v>
       </c>
       <c r="J35">
-        <v>87.096</v>
+        <v>1.68</v>
       </c>
       <c r="K35" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L35" s="1">
         <v>95.76000000000001</v>
       </c>
-      <c r="M35" t="s">
-        <v>107</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="L35" t="s">
+        <v>106</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36">
         <v>40.69</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H36">
         <v>1.564</v>
       </c>
       <c r="I36" s="1">
-        <v>1.564</v>
+        <v>63.639</v>
       </c>
       <c r="J36">
-        <v>63.63916</v>
+        <v>1.68</v>
       </c>
       <c r="K36" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L36" s="1">
-        <v>68.3592</v>
-      </c>
-      <c r="M36" t="s">
-        <v>108</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>68.35899999999999</v>
+      </c>
+      <c r="L36" t="s">
+        <v>107</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37">
         <v>19</v>
       </c>
       <c r="D37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" t="s">
         <v>69</v>
-      </c>
-      <c r="E37" t="s">
-        <v>70</v>
       </c>
       <c r="F37">
         <v>41.411</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H37">
         <v>1.564</v>
       </c>
       <c r="I37" s="1">
-        <v>1.564</v>
+        <v>64.767</v>
       </c>
       <c r="J37">
-        <v>64.76680399999999</v>
+        <v>1.68</v>
       </c>
       <c r="K37" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L37" s="1">
-        <v>69.57048</v>
-      </c>
-      <c r="M37" t="s">
-        <v>109</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="L37" t="s">
+        <v>108</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38">
         <v>60.059</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H38">
         <v>1.588</v>
       </c>
       <c r="I38" s="1">
-        <v>1.588</v>
+        <v>95.374</v>
       </c>
       <c r="J38">
-        <v>95.37369200000001</v>
+        <v>1.69</v>
       </c>
       <c r="K38" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L38" s="1">
-        <v>101.49971</v>
-      </c>
-      <c r="M38" t="s">
-        <v>110</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>101.5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>109</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39">
         <v>8.840999999999999</v>
       </c>
       <c r="G39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H39">
         <v>1.588</v>
       </c>
       <c r="I39" s="1">
-        <v>1.588</v>
+        <v>14.04</v>
       </c>
       <c r="J39">
-        <v>14.039508</v>
+        <v>1.7</v>
       </c>
       <c r="K39" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L39" s="1">
-        <v>15.0297</v>
-      </c>
-      <c r="M39" t="s">
-        <v>111</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+        <v>15.03</v>
+      </c>
+      <c r="L39" t="s">
+        <v>110</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F40">
         <v>46.78</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H40">
         <v>1.649</v>
       </c>
       <c r="I40" s="1">
-        <v>1.649</v>
+        <v>77.14</v>
       </c>
       <c r="J40">
-        <v>77.14022</v>
+        <v>1.82</v>
       </c>
       <c r="K40" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L40" s="1">
-        <v>85.1396</v>
-      </c>
-      <c r="M40" t="s">
-        <v>112</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>85.14</v>
+      </c>
+      <c r="L40" t="s">
+        <v>111</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F41">
         <v>18.558</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41">
         <v>1.401</v>
       </c>
       <c r="I41" s="1">
-        <v>1.401</v>
+        <v>26</v>
       </c>
       <c r="J41">
-        <v>25.999758</v>
+        <v>1.56</v>
       </c>
       <c r="K41" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L41" s="1">
-        <v>28.95048</v>
-      </c>
-      <c r="M41" t="s">
-        <v>113</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>28.95</v>
+      </c>
+      <c r="L41" t="s">
+        <v>112</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42">
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42">
         <v>12.859</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H42">
         <v>0.64</v>
       </c>
       <c r="I42" s="1">
+        <v>8.23</v>
+      </c>
+      <c r="J42">
         <v>0.64</v>
       </c>
-      <c r="J42">
-        <v>8.229760000000001</v>
-      </c>
       <c r="K42" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L42" s="1">
-        <v>8.229760000000001</v>
-      </c>
-      <c r="M42" t="s">
-        <v>113</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>8.23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>112</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F43">
         <v>22.869</v>
       </c>
       <c r="G43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H43">
         <v>1.619</v>
       </c>
       <c r="I43" s="1">
-        <v>1.619</v>
+        <v>37.025</v>
       </c>
       <c r="J43">
-        <v>37.024911</v>
+        <v>1.75</v>
       </c>
       <c r="K43" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L43" s="1">
-        <v>40.02075</v>
-      </c>
-      <c r="M43" t="s">
-        <v>114</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>40.021</v>
+      </c>
+      <c r="L43" t="s">
+        <v>113</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F44">
         <v>23.899</v>
       </c>
       <c r="G44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H44">
         <v>1.401</v>
       </c>
       <c r="I44" s="1">
-        <v>1.401</v>
+        <v>33.482</v>
       </c>
       <c r="J44">
-        <v>33.482499</v>
+        <v>1.59</v>
       </c>
       <c r="K44" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="L44" s="1">
-        <v>37.99941</v>
-      </c>
-      <c r="M44" t="s">
-        <v>78</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>37.999</v>
+      </c>
+      <c r="L44" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45">
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>45.731</v>
       </c>
       <c r="G45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H45">
         <v>1.619</v>
       </c>
       <c r="I45" s="1">
-        <v>1.619</v>
+        <v>74.038</v>
       </c>
       <c r="J45">
-        <v>74.038489</v>
+        <v>1.75</v>
       </c>
       <c r="K45" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L45" s="1">
-        <v>80.02925</v>
-      </c>
-      <c r="M45" t="s">
-        <v>115</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>80.029</v>
+      </c>
+      <c r="L45" t="s">
+        <v>114</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F46">
         <v>55.12</v>
       </c>
       <c r="G46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H46">
         <v>1.653</v>
       </c>
       <c r="I46" s="1">
-        <v>1.653</v>
+        <v>91.113</v>
       </c>
       <c r="J46">
-        <v>91.11336</v>
+        <v>1.75</v>
       </c>
       <c r="K46" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L46" s="1">
         <v>96.45999999999999</v>
       </c>
-      <c r="M46" t="s">
-        <v>116</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="L46" t="s">
+        <v>115</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47">
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F47">
         <v>28.955</v>
       </c>
       <c r="G47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H47">
         <v>1.449</v>
       </c>
       <c r="I47" s="1">
-        <v>1.449</v>
+        <v>41.956</v>
       </c>
       <c r="J47">
-        <v>41.955795</v>
+        <v>1.55</v>
       </c>
       <c r="K47" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L47" s="1">
-        <v>44.88025</v>
-      </c>
-      <c r="M47" t="s">
-        <v>117</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+        <v>44.88</v>
+      </c>
+      <c r="L47" t="s">
+        <v>116</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48">
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48">
         <v>20.547</v>
       </c>
       <c r="G48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H48">
         <v>0.64</v>
       </c>
       <c r="I48" s="1">
+        <v>13.15</v>
+      </c>
+      <c r="J48">
         <v>0.64</v>
       </c>
-      <c r="J48">
-        <v>13.15008</v>
-      </c>
       <c r="K48" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L48" s="1">
-        <v>13.15008</v>
-      </c>
-      <c r="M48" t="s">
-        <v>117</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>13.15</v>
+      </c>
+      <c r="L48" t="s">
+        <v>116</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49">
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F49">
         <v>22.516</v>
       </c>
       <c r="G49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H49">
         <v>0.64</v>
       </c>
       <c r="I49" s="1">
+        <v>14.41</v>
+      </c>
+      <c r="J49">
         <v>0.64</v>
       </c>
-      <c r="J49">
-        <v>14.41024</v>
-      </c>
       <c r="K49" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L49" s="1">
-        <v>14.41024</v>
-      </c>
-      <c r="M49" t="s">
-        <v>118</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49" t="s">
+        <v>14.41</v>
+      </c>
+      <c r="L49" t="s">
+        <v>117</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="3" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
-      <c r="A52" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3246,149 +3096,149 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:14">
       <c r="A53" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="E53" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" s="6">
         <v>1110.165</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="7">
         <v>25</v>
       </c>
       <c r="D54" s="7">
-        <v>1.479506</v>
-      </c>
-      <c r="E54" s="6">
-        <v>1642.5</v>
-      </c>
-      <c r="F54" s="6">
+        <v>1.48</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1642.497</v>
+      </c>
+      <c r="F54" s="7">
         <v>1779.17</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:14">
       <c r="A55" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" s="6">
         <v>435.188</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="7">
         <v>11</v>
       </c>
       <c r="D55" s="7">
-        <v>1.370446</v>
-      </c>
-      <c r="E55" s="6">
-        <v>596.4</v>
-      </c>
-      <c r="F55" s="6">
+        <v>1.37</v>
+      </c>
+      <c r="E55" s="7">
+        <v>596.402</v>
+      </c>
+      <c r="F55" s="7">
         <v>659.51</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:14">
       <c r="A56" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="6">
         <v>205.718</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="7">
         <v>4</v>
       </c>
       <c r="D56" s="7">
-        <v>1.633548</v>
-      </c>
-      <c r="E56" s="6">
+        <v>1.634</v>
+      </c>
+      <c r="E56" s="7">
         <v>336.05</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="7">
         <v>364.57</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:14">
       <c r="A57" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B57" s="6">
         <v>79.828</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="7">
         <v>4</v>
       </c>
       <c r="D57" s="7">
         <v>0.64</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="7">
         <v>51.09</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="7">
         <v>51.09</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:14">
       <c r="A58" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" s="6">
         <v>10.441</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="7">
         <v>1</v>
       </c>
       <c r="D58" s="7">
         <v>1.27</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="7">
         <v>13.26</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="7">
         <v>13.26</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:14">
       <c r="A59" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B59" s="6">
         <v>8</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="7">
         <v>3</v>
       </c>
       <c r="D59" s="7">
         <v>4.99</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E59" s="7">
         <v>39.92</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="7">
         <v>39.92</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:14">
       <c r="A60" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B60" s="9">
         <v>1849.34</v>
@@ -3398,7 +3248,7 @@
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="9">
-        <v>2679.22</v>
+        <v>2679.219</v>
       </c>
       <c r="F60" s="9">
         <v>2907.52</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0651B55DA6F78DC6393DAC89F266DDB667404BF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D9EE592-1780-42D2-ADCC-46BEA74EBDC4}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ДЖИ ТИ ЕЙ ПЕТРОЛИУМ" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ДЖИ ТИ ЕЙ ПЕТРОЛИУМ'!$A$1:$N$49</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="166">
   <si>
     <t>Дата</t>
   </si>
@@ -517,12 +526,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,30 +614,38 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -667,7 +683,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -701,6 +717,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -735,9 +752,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -910,9 +928,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -930,7 +949,7 @@
     <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -974,7 +993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -991,7 +1010,7 @@
         <v>69</v>
       </c>
       <c r="F2">
-        <v>38.292</v>
+        <v>38.292000000000002</v>
       </c>
       <c r="G2" t="s">
         <v>75</v>
@@ -1000,7 +1019,7 @@
         <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>53.571</v>
+        <v>53.570999999999998</v>
       </c>
       <c r="J2">
         <v>1.54</v>
@@ -1018,7 +1037,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1035,7 +1054,7 @@
         <v>69</v>
       </c>
       <c r="F3">
-        <v>63.279</v>
+        <v>63.279000000000003</v>
       </c>
       <c r="G3" t="s">
         <v>75</v>
@@ -1044,7 +1063,7 @@
         <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>88.527</v>
+        <v>88.527000000000001</v>
       </c>
       <c r="J3">
         <v>1.54</v>
@@ -1062,7 +1081,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1079,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="F4">
-        <v>23.906</v>
+        <v>23.905999999999999</v>
       </c>
       <c r="G4" t="s">
         <v>75</v>
@@ -1106,7 +1125,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1123,16 +1142,16 @@
         <v>69</v>
       </c>
       <c r="F5">
-        <v>50.579</v>
+        <v>50.579000000000001</v>
       </c>
       <c r="G5" t="s">
         <v>75</v>
       </c>
       <c r="H5">
-        <v>1.406</v>
+        <v>1.4059999999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>71.114</v>
+        <v>71.114000000000004</v>
       </c>
       <c r="J5">
         <v>1.52</v>
@@ -1150,7 +1169,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1167,22 +1186,22 @@
         <v>69</v>
       </c>
       <c r="F6">
-        <v>56.513</v>
+        <v>56.512999999999998</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
       </c>
       <c r="H6">
-        <v>1.406</v>
+        <v>1.4059999999999999</v>
       </c>
       <c r="I6" s="1">
-        <v>79.45699999999999</v>
+        <v>79.456999999999994</v>
       </c>
       <c r="J6">
         <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>85.90000000000001</v>
+        <v>85.9</v>
       </c>
       <c r="L6" t="s">
         <v>81</v>
@@ -1194,7 +1213,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1211,7 +1230,7 @@
         <v>71</v>
       </c>
       <c r="F7">
-        <v>55.333</v>
+        <v>55.332999999999998</v>
       </c>
       <c r="G7" t="s">
         <v>75</v>
@@ -1220,7 +1239,7 @@
         <v>1.359</v>
       </c>
       <c r="I7" s="1">
-        <v>75.19799999999999</v>
+        <v>75.197999999999993</v>
       </c>
       <c r="J7">
         <v>1.5</v>
@@ -1238,7 +1257,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1255,16 +1274,16 @@
         <v>69</v>
       </c>
       <c r="F8">
-        <v>41.719</v>
+        <v>41.719000000000001</v>
       </c>
       <c r="G8" t="s">
         <v>75</v>
       </c>
       <c r="H8">
-        <v>1.406</v>
+        <v>1.4059999999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>58.657</v>
+        <v>58.656999999999996</v>
       </c>
       <c r="J8">
         <v>1.53</v>
@@ -1282,7 +1301,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1299,22 +1318,22 @@
         <v>69</v>
       </c>
       <c r="F9">
-        <v>45.862</v>
+        <v>45.862000000000002</v>
       </c>
       <c r="G9" t="s">
         <v>75</v>
       </c>
       <c r="H9">
-        <v>1.406</v>
+        <v>1.4059999999999999</v>
       </c>
       <c r="I9" s="1">
-        <v>64.482</v>
+        <v>64.481999999999999</v>
       </c>
       <c r="J9">
         <v>1.52</v>
       </c>
       <c r="K9" s="1">
-        <v>69.70999999999999</v>
+        <v>69.709999999999994</v>
       </c>
       <c r="L9" t="s">
         <v>84</v>
@@ -1326,7 +1345,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1349,10 +1368,10 @@
         <v>75</v>
       </c>
       <c r="H10">
-        <v>1.406</v>
+        <v>1.4059999999999999</v>
       </c>
       <c r="I10" s="1">
-        <v>92.79600000000001</v>
+        <v>92.796000000000006</v>
       </c>
       <c r="J10">
         <v>1.56</v>
@@ -1370,7 +1389,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1396,7 +1415,7 @@
         <v>1.359</v>
       </c>
       <c r="I11" s="1">
-        <v>79.166</v>
+        <v>79.165999999999997</v>
       </c>
       <c r="J11">
         <v>1.5</v>
@@ -1414,7 +1433,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1458,7 +1477,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1475,7 +1494,7 @@
         <v>71</v>
       </c>
       <c r="F13">
-        <v>26.053</v>
+        <v>26.053000000000001</v>
       </c>
       <c r="G13" t="s">
         <v>75</v>
@@ -1484,13 +1503,13 @@
         <v>1.359</v>
       </c>
       <c r="I13" s="1">
-        <v>35.406</v>
+        <v>35.405999999999999</v>
       </c>
       <c r="J13">
         <v>1.52</v>
       </c>
       <c r="K13" s="1">
-        <v>39.601</v>
+        <v>39.600999999999999</v>
       </c>
       <c r="L13" t="s">
         <v>87</v>
@@ -1502,7 +1521,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1525,10 +1544,10 @@
         <v>75</v>
       </c>
       <c r="H14">
-        <v>1.412</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="I14" s="1">
-        <v>40.365</v>
+        <v>40.365000000000002</v>
       </c>
       <c r="J14">
         <v>1.55</v>
@@ -1546,7 +1565,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1563,13 +1582,13 @@
         <v>69</v>
       </c>
       <c r="F15">
-        <v>41.289</v>
+        <v>41.289000000000001</v>
       </c>
       <c r="G15" t="s">
         <v>75</v>
       </c>
       <c r="H15">
-        <v>1.412</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="I15" s="1">
         <v>58.3</v>
@@ -1590,7 +1609,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1616,7 +1635,7 @@
         <v>1.629</v>
       </c>
       <c r="I16" s="1">
-        <v>108.817</v>
+        <v>108.81699999999999</v>
       </c>
       <c r="J16">
         <v>1.75</v>
@@ -1634,7 +1653,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1651,13 +1670,13 @@
         <v>69</v>
       </c>
       <c r="F17">
-        <v>42.783</v>
+        <v>42.783000000000001</v>
       </c>
       <c r="G17" t="s">
         <v>75</v>
       </c>
       <c r="H17">
-        <v>1.412</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="I17" s="1">
         <v>60.41</v>
@@ -1678,7 +1697,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1695,7 +1714,7 @@
         <v>71</v>
       </c>
       <c r="F18">
-        <v>63.487</v>
+        <v>63.487000000000002</v>
       </c>
       <c r="G18" t="s">
         <v>75</v>
@@ -1704,7 +1723,7 @@
         <v>1.359</v>
       </c>
       <c r="I18" s="1">
-        <v>86.279</v>
+        <v>86.278999999999996</v>
       </c>
       <c r="J18">
         <v>1.52</v>
@@ -1722,7 +1741,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1745,10 +1764,10 @@
         <v>75</v>
       </c>
       <c r="H19">
-        <v>1.437</v>
+        <v>1.4370000000000001</v>
       </c>
       <c r="I19" s="1">
-        <v>79.22799999999999</v>
+        <v>79.227999999999994</v>
       </c>
       <c r="J19">
         <v>1.57</v>
@@ -1766,7 +1785,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1810,7 +1829,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1846,7 @@
         <v>73</v>
       </c>
       <c r="F21">
-        <v>36.729</v>
+        <v>36.728999999999999</v>
       </c>
       <c r="G21" t="s">
         <v>75</v>
@@ -1836,13 +1855,13 @@
         <v>1.629</v>
       </c>
       <c r="I21" s="1">
-        <v>59.832</v>
+        <v>59.832000000000001</v>
       </c>
       <c r="J21">
         <v>1.77</v>
       </c>
       <c r="K21" s="1">
-        <v>65.01000000000001</v>
+        <v>65.010000000000005</v>
       </c>
       <c r="L21" t="s">
         <v>94</v>
@@ -1854,7 +1873,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1871,7 +1890,7 @@
         <v>71</v>
       </c>
       <c r="F22">
-        <v>46.557</v>
+        <v>46.557000000000002</v>
       </c>
       <c r="G22" t="s">
         <v>75</v>
@@ -1880,7 +1899,7 @@
         <v>1.359</v>
       </c>
       <c r="I22" s="1">
-        <v>63.271</v>
+        <v>63.271000000000001</v>
       </c>
       <c r="J22">
         <v>1.49</v>
@@ -1898,7 +1917,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1915,16 +1934,16 @@
         <v>69</v>
       </c>
       <c r="F23">
-        <v>54.418</v>
+        <v>54.417999999999999</v>
       </c>
       <c r="G23" t="s">
         <v>75</v>
       </c>
       <c r="H23">
-        <v>1.437</v>
+        <v>1.4370000000000001</v>
       </c>
       <c r="I23" s="1">
-        <v>78.199</v>
+        <v>78.198999999999998</v>
       </c>
       <c r="J23">
         <v>1.58</v>
@@ -1942,7 +1961,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1959,7 +1978,7 @@
         <v>74</v>
       </c>
       <c r="F24">
-        <v>10.441</v>
+        <v>10.441000000000001</v>
       </c>
       <c r="G24" t="s">
         <v>75</v>
@@ -1986,7 +2005,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2003,7 +2022,7 @@
         <v>73</v>
       </c>
       <c r="F25">
-        <v>55.409</v>
+        <v>55.408999999999999</v>
       </c>
       <c r="G25" t="s">
         <v>75</v>
@@ -2012,7 +2031,7 @@
         <v>1.629</v>
       </c>
       <c r="I25" s="1">
-        <v>90.261</v>
+        <v>90.260999999999996</v>
       </c>
       <c r="J25">
         <v>1.76</v>
@@ -2030,7 +2049,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2047,7 +2066,7 @@
         <v>71</v>
       </c>
       <c r="F26">
-        <v>54.873</v>
+        <v>54.872999999999998</v>
       </c>
       <c r="G26" t="s">
         <v>75</v>
@@ -2056,7 +2075,7 @@
         <v>1.359</v>
       </c>
       <c r="I26" s="1">
-        <v>74.572</v>
+        <v>74.572000000000003</v>
       </c>
       <c r="J26">
         <v>1.5</v>
@@ -2074,7 +2093,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2091,13 +2110,13 @@
         <v>69</v>
       </c>
       <c r="F27">
-        <v>49.013</v>
+        <v>49.012999999999998</v>
       </c>
       <c r="G27" t="s">
         <v>75</v>
       </c>
       <c r="H27">
-        <v>1.489</v>
+        <v>1.4890000000000001</v>
       </c>
       <c r="I27" s="1">
         <v>72.98</v>
@@ -2106,7 +2125,7 @@
         <v>1.58</v>
       </c>
       <c r="K27" s="1">
-        <v>77.441</v>
+        <v>77.441000000000003</v>
       </c>
       <c r="L27" t="s">
         <v>99</v>
@@ -2118,7 +2137,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2135,7 +2154,7 @@
         <v>71</v>
       </c>
       <c r="F28">
-        <v>24.733</v>
+        <v>24.733000000000001</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
@@ -2144,7 +2163,7 @@
         <v>1.369</v>
       </c>
       <c r="I28" s="1">
-        <v>33.859</v>
+        <v>33.859000000000002</v>
       </c>
       <c r="J28">
         <v>1.5</v>
@@ -2162,7 +2181,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2206,7 +2225,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -2223,16 +2242,16 @@
         <v>69</v>
       </c>
       <c r="F30">
-        <v>48.758</v>
+        <v>48.758000000000003</v>
       </c>
       <c r="G30" t="s">
         <v>75</v>
       </c>
       <c r="H30">
-        <v>1.499</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="I30" s="1">
-        <v>73.08799999999999</v>
+        <v>73.087999999999994</v>
       </c>
       <c r="J30">
         <v>1.61</v>
@@ -2250,7 +2269,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -2267,16 +2286,16 @@
         <v>69</v>
       </c>
       <c r="F31">
-        <v>33.733</v>
+        <v>33.732999999999997</v>
       </c>
       <c r="G31" t="s">
         <v>75</v>
       </c>
       <c r="H31">
-        <v>1.499</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="I31" s="1">
-        <v>50.566</v>
+        <v>50.566000000000003</v>
       </c>
       <c r="J31">
         <v>1.61</v>
@@ -2294,7 +2313,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -2311,22 +2330,22 @@
         <v>69</v>
       </c>
       <c r="F32">
-        <v>21.982</v>
+        <v>21.981999999999999</v>
       </c>
       <c r="G32" t="s">
         <v>75</v>
       </c>
       <c r="H32">
-        <v>1.499</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="I32" s="1">
-        <v>32.951</v>
+        <v>32.951000000000001</v>
       </c>
       <c r="J32">
         <v>1.63</v>
       </c>
       <c r="K32" s="1">
-        <v>35.831</v>
+        <v>35.831000000000003</v>
       </c>
       <c r="L32" t="s">
         <v>103</v>
@@ -2338,7 +2357,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -2361,10 +2380,10 @@
         <v>75</v>
       </c>
       <c r="H33">
-        <v>1.499</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="I33" s="1">
-        <v>60.714</v>
+        <v>60.713999999999999</v>
       </c>
       <c r="J33">
         <v>1.63</v>
@@ -2382,7 +2401,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2399,7 +2418,7 @@
         <v>71</v>
       </c>
       <c r="F34">
-        <v>34.487</v>
+        <v>34.487000000000002</v>
       </c>
       <c r="G34" t="s">
         <v>75</v>
@@ -2408,7 +2427,7 @@
         <v>1.369</v>
       </c>
       <c r="I34" s="1">
-        <v>47.213</v>
+        <v>47.213000000000001</v>
       </c>
       <c r="J34">
         <v>1.52</v>
@@ -2426,7 +2445,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2452,13 +2471,13 @@
         <v>1.528</v>
       </c>
       <c r="I35" s="1">
-        <v>87.096</v>
+        <v>87.096000000000004</v>
       </c>
       <c r="J35">
         <v>1.68</v>
       </c>
       <c r="K35" s="1">
-        <v>95.76000000000001</v>
+        <v>95.76</v>
       </c>
       <c r="L35" t="s">
         <v>106</v>
@@ -2470,7 +2489,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2493,16 +2512,16 @@
         <v>75</v>
       </c>
       <c r="H36">
-        <v>1.564</v>
+        <v>1.5640000000000001</v>
       </c>
       <c r="I36" s="1">
-        <v>63.639</v>
+        <v>63.639000000000003</v>
       </c>
       <c r="J36">
         <v>1.68</v>
       </c>
       <c r="K36" s="1">
-        <v>68.35899999999999</v>
+        <v>68.358999999999995</v>
       </c>
       <c r="L36" t="s">
         <v>107</v>
@@ -2514,7 +2533,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -2531,22 +2550,22 @@
         <v>69</v>
       </c>
       <c r="F37">
-        <v>41.411</v>
+        <v>41.411000000000001</v>
       </c>
       <c r="G37" t="s">
         <v>75</v>
       </c>
       <c r="H37">
-        <v>1.564</v>
+        <v>1.5640000000000001</v>
       </c>
       <c r="I37" s="1">
-        <v>64.767</v>
+        <v>64.766999999999996</v>
       </c>
       <c r="J37">
         <v>1.68</v>
       </c>
       <c r="K37" s="1">
-        <v>69.56999999999999</v>
+        <v>69.569999999999993</v>
       </c>
       <c r="L37" t="s">
         <v>108</v>
@@ -2558,7 +2577,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -2575,16 +2594,16 @@
         <v>69</v>
       </c>
       <c r="F38">
-        <v>60.059</v>
+        <v>60.058999999999997</v>
       </c>
       <c r="G38" t="s">
         <v>75</v>
       </c>
       <c r="H38">
-        <v>1.588</v>
+        <v>1.5880000000000001</v>
       </c>
       <c r="I38" s="1">
-        <v>95.374</v>
+        <v>95.373999999999995</v>
       </c>
       <c r="J38">
         <v>1.69</v>
@@ -2602,7 +2621,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -2619,13 +2638,13 @@
         <v>69</v>
       </c>
       <c r="F39">
-        <v>8.840999999999999</v>
+        <v>8.8409999999999993</v>
       </c>
       <c r="G39" t="s">
         <v>75</v>
       </c>
       <c r="H39">
-        <v>1.588</v>
+        <v>1.5880000000000001</v>
       </c>
       <c r="I39" s="1">
         <v>14.04</v>
@@ -2646,7 +2665,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -2690,7 +2709,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -2734,7 +2753,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -2778,7 +2797,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -2804,13 +2823,13 @@
         <v>1.619</v>
       </c>
       <c r="I43" s="1">
-        <v>37.025</v>
+        <v>37.024999999999999</v>
       </c>
       <c r="J43">
         <v>1.75</v>
       </c>
       <c r="K43" s="1">
-        <v>40.021</v>
+        <v>40.021000000000001</v>
       </c>
       <c r="L43" t="s">
         <v>113</v>
@@ -2822,7 +2841,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -2839,7 +2858,7 @@
         <v>71</v>
       </c>
       <c r="F44">
-        <v>23.899</v>
+        <v>23.899000000000001</v>
       </c>
       <c r="G44" t="s">
         <v>75</v>
@@ -2848,13 +2867,13 @@
         <v>1.401</v>
       </c>
       <c r="I44" s="1">
-        <v>33.482</v>
+        <v>33.481999999999999</v>
       </c>
       <c r="J44">
         <v>1.59</v>
       </c>
       <c r="K44" s="1">
-        <v>37.999</v>
+        <v>37.999000000000002</v>
       </c>
       <c r="L44" t="s">
         <v>77</v>
@@ -2866,7 +2885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -2883,7 +2902,7 @@
         <v>69</v>
       </c>
       <c r="F45">
-        <v>45.731</v>
+        <v>45.731000000000002</v>
       </c>
       <c r="G45" t="s">
         <v>75</v>
@@ -2892,13 +2911,13 @@
         <v>1.619</v>
       </c>
       <c r="I45" s="1">
-        <v>74.038</v>
+        <v>74.037999999999997</v>
       </c>
       <c r="J45">
         <v>1.75</v>
       </c>
       <c r="K45" s="1">
-        <v>80.029</v>
+        <v>80.028999999999996</v>
       </c>
       <c r="L45" t="s">
         <v>114</v>
@@ -2910,7 +2929,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -2942,7 +2961,7 @@
         <v>1.75</v>
       </c>
       <c r="K46" s="1">
-        <v>96.45999999999999</v>
+        <v>96.46</v>
       </c>
       <c r="L46" t="s">
         <v>115</v>
@@ -2954,7 +2973,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>35</v>
       </c>
@@ -2971,16 +2990,16 @@
         <v>71</v>
       </c>
       <c r="F47">
-        <v>28.955</v>
+        <v>28.954999999999998</v>
       </c>
       <c r="G47" t="s">
         <v>75</v>
       </c>
       <c r="H47">
-        <v>1.449</v>
+        <v>1.4490000000000001</v>
       </c>
       <c r="I47" s="1">
-        <v>41.956</v>
+        <v>41.956000000000003</v>
       </c>
       <c r="J47">
         <v>1.55</v>
@@ -2998,7 +3017,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -3015,7 +3034,7 @@
         <v>70</v>
       </c>
       <c r="F48">
-        <v>20.547</v>
+        <v>20.547000000000001</v>
       </c>
       <c r="G48" t="s">
         <v>75</v>
@@ -3042,7 +3061,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>35</v>
       </c>
@@ -3059,7 +3078,7 @@
         <v>70</v>
       </c>
       <c r="F49">
-        <v>22.516</v>
+        <v>22.515999999999998</v>
       </c>
       <c r="G49" t="s">
         <v>75</v>
@@ -3086,175 +3105,182 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="3" t="s">
+    <row r="52" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="4" t="s">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="5">
         <v>1110.165</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="6">
         <v>25</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>1.48</v>
       </c>
-      <c r="E54" s="7">
-        <v>1642.497</v>
-      </c>
-      <c r="F54" s="7">
+      <c r="E54" s="6">
+        <v>1642.4970000000001</v>
+      </c>
+      <c r="F54" s="6">
         <v>1779.17</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="6">
-        <v>435.188</v>
-      </c>
-      <c r="C55" s="7">
+      <c r="B55" s="5">
+        <v>435.18799999999999</v>
+      </c>
+      <c r="C55" s="6">
         <v>11</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>1.37</v>
       </c>
-      <c r="E55" s="7">
-        <v>596.402</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="E55" s="6">
+        <v>596.40200000000004</v>
+      </c>
+      <c r="F55" s="6">
         <v>659.51</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="6">
-        <v>205.718</v>
-      </c>
-      <c r="C56" s="7">
+      <c r="B56" s="5">
+        <v>205.71799999999999</v>
+      </c>
+      <c r="C56" s="6">
         <v>4</v>
       </c>
-      <c r="D56" s="7">
-        <v>1.634</v>
-      </c>
-      <c r="E56" s="7">
+      <c r="D56" s="6">
+        <v>1.6339999999999999</v>
+      </c>
+      <c r="E56" s="6">
         <v>336.05</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="6">
         <v>364.57</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="6">
-        <v>79.828</v>
-      </c>
-      <c r="C57" s="7">
+      <c r="B57" s="5">
+        <v>79.828000000000003</v>
+      </c>
+      <c r="C57" s="6">
         <v>4</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>0.64</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="6">
         <v>51.09</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="6">
         <v>51.09</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="6">
-        <v>10.441</v>
-      </c>
-      <c r="C58" s="7">
+      <c r="B58" s="5">
+        <v>10.441000000000001</v>
+      </c>
+      <c r="C58" s="6">
         <v>1</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="6">
         <v>1.27</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="6">
         <v>13.26</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="6">
         <v>13.26</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="5">
         <v>8</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="6">
         <v>3</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="6">
         <v>4.99</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="6">
         <v>39.92</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="6">
         <v>39.92</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="8" t="s">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="8">
         <v>1849.34</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>48</v>
       </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="9">
-        <v>2679.219</v>
-      </c>
-      <c r="F60" s="9">
+      <c r="D60" s="6"/>
+      <c r="E60" s="8">
+        <v>2679.2190000000001</v>
+      </c>
+      <c r="F60" s="8">
         <v>2907.52</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N49" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="78970110027720092"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A52:F52"/>
   </mergeCells>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ/ДЖИ ТИ ЕЙ ПЕТРОЛИУМ.xlsx
@@ -946,10 +946,10 @@
         <v>72</v>
       </c>
       <c r="H2" s="1">
-        <v>1.689</v>
+        <v>1.69</v>
       </c>
       <c r="I2" s="1">
-        <v>74.265</v>
+        <v>74.309</v>
       </c>
       <c r="J2" s="1">
         <v>1.79</v>
@@ -990,10 +990,10 @@
         <v>72</v>
       </c>
       <c r="H3" s="1">
-        <v>1.459</v>
+        <v>1.46</v>
       </c>
       <c r="I3" s="1">
-        <v>63.612</v>
+        <v>63.656</v>
       </c>
       <c r="J3" s="1">
         <v>1.55</v>
@@ -1034,10 +1034,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I4" s="1">
-        <v>102.898</v>
+        <v>103.079</v>
       </c>
       <c r="J4" s="1">
         <v>1.82</v>
@@ -1122,10 +1122,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="1">
-        <v>1.459</v>
+        <v>1.46</v>
       </c>
       <c r="I6" s="1">
-        <v>43.493</v>
+        <v>43.523</v>
       </c>
       <c r="J6" s="1">
         <v>1.58</v>
@@ -1166,10 +1166,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="1">
-        <v>1.459</v>
+        <v>1.46</v>
       </c>
       <c r="I7" s="1">
-        <v>51.298</v>
+        <v>51.334</v>
       </c>
       <c r="J7" s="1">
         <v>1.55</v>
@@ -1210,10 +1210,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I8" s="1">
-        <v>78.19799999999999</v>
+        <v>78.33499999999999</v>
       </c>
       <c r="J8" s="1">
         <v>1.79</v>
@@ -1254,10 +1254,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I9" s="1">
-        <v>93.691</v>
+        <v>93.52500000000001</v>
       </c>
       <c r="J9" s="1">
         <v>1.81</v>
@@ -1298,10 +1298,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="1">
-        <v>1.449</v>
+        <v>1.45</v>
       </c>
       <c r="I10" s="1">
-        <v>27.792</v>
+        <v>27.811</v>
       </c>
       <c r="J10" s="1">
         <v>1.55</v>
@@ -1342,10 +1342,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I11" s="1">
-        <v>48.42</v>
+        <v>48.334</v>
       </c>
       <c r="J11" s="1">
         <v>1.8</v>
@@ -1386,10 +1386,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I12" s="1">
-        <v>77.15000000000001</v>
+        <v>77.01300000000001</v>
       </c>
       <c r="J12" s="1">
         <v>1.8</v>
@@ -1430,10 +1430,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="1">
-        <v>1.674</v>
+        <v>1.67</v>
       </c>
       <c r="I13" s="1">
-        <v>95.435</v>
+        <v>95.20699999999999</v>
       </c>
       <c r="J13" s="1">
         <v>1.8</v>
@@ -1474,10 +1474,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="1">
-        <v>1.674</v>
+        <v>1.67</v>
       </c>
       <c r="I14" s="1">
-        <v>95.01600000000001</v>
+        <v>94.789</v>
       </c>
       <c r="J14" s="1">
         <v>1.83</v>
@@ -1518,10 +1518,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="1">
-        <v>1.686</v>
+        <v>1.69</v>
       </c>
       <c r="I15" s="1">
-        <v>109.792</v>
+        <v>110.053</v>
       </c>
       <c r="J15" s="1">
         <v>1.81</v>
@@ -1562,10 +1562,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="1">
-        <v>1.674</v>
+        <v>1.67</v>
       </c>
       <c r="I16" s="1">
-        <v>53.986</v>
+        <v>53.857</v>
       </c>
       <c r="J16" s="1">
         <v>1.82</v>
@@ -1606,10 +1606,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="1">
-        <v>1.687</v>
+        <v>1.69</v>
       </c>
       <c r="I17" s="1">
-        <v>73.41800000000001</v>
+        <v>73.54900000000001</v>
       </c>
       <c r="J17" s="1">
         <v>1.79</v>
@@ -1650,10 +1650,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="1">
-        <v>1.686</v>
+        <v>1.69</v>
       </c>
       <c r="I18" s="1">
-        <v>76.325</v>
+        <v>76.506</v>
       </c>
       <c r="J18" s="1">
         <v>1.82</v>
@@ -1738,10 +1738,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="1">
-        <v>1.687</v>
+        <v>1.69</v>
       </c>
       <c r="I20" s="1">
-        <v>78.8</v>
+        <v>78.94</v>
       </c>
       <c r="J20" s="1">
         <v>1.82</v>
@@ -1826,10 +1826,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="1">
-        <v>1.687</v>
+        <v>1.69</v>
       </c>
       <c r="I22" s="1">
-        <v>67.48</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J22" s="1">
         <v>1.8</v>
@@ -1870,10 +1870,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I23" s="1">
-        <v>73.333</v>
+        <v>73.462</v>
       </c>
       <c r="J23" s="1">
         <v>1.84</v>
@@ -2002,10 +2002,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="1">
-        <v>1.719</v>
+        <v>1.72</v>
       </c>
       <c r="I26" s="1">
-        <v>93.44499999999999</v>
+        <v>93.499</v>
       </c>
       <c r="J26" s="1">
         <v>1.84</v>
@@ -2046,10 +2046,10 @@
         <v>72</v>
       </c>
       <c r="H27" s="1">
-        <v>1.738</v>
+        <v>1.74</v>
       </c>
       <c r="I27" s="1">
-        <v>73.83</v>
+        <v>73.91500000000001</v>
       </c>
       <c r="J27" s="1">
         <v>1.85</v>
@@ -2090,10 +2090,10 @@
         <v>72</v>
       </c>
       <c r="H28" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I28" s="1">
-        <v>55.706</v>
+        <v>55.738</v>
       </c>
       <c r="J28" s="1">
         <v>1.85</v>
@@ -2134,10 +2134,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I29" s="1">
-        <v>88.569</v>
+        <v>88.62</v>
       </c>
       <c r="J29" s="1">
         <v>1.86</v>
@@ -2178,10 +2178,10 @@
         <v>72</v>
       </c>
       <c r="H30" s="1">
-        <v>1.489</v>
+        <v>1.49</v>
       </c>
       <c r="I30" s="1">
-        <v>56.165</v>
+        <v>56.203</v>
       </c>
       <c r="J30" s="1">
         <v>1.59</v>
@@ -2266,10 +2266,10 @@
         <v>72</v>
       </c>
       <c r="H32" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I32" s="1">
-        <v>94.761</v>
+        <v>94.815</v>
       </c>
       <c r="J32" s="1">
         <v>1.86</v>
@@ -2310,10 +2310,10 @@
         <v>72</v>
       </c>
       <c r="H33" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I33" s="1">
-        <v>99.693</v>
+        <v>99.75</v>
       </c>
       <c r="J33" s="1">
         <v>1.84</v>
@@ -2354,10 +2354,10 @@
         <v>72</v>
       </c>
       <c r="H34" s="1">
-        <v>1.729</v>
+        <v>1.73</v>
       </c>
       <c r="I34" s="1">
-        <v>48.187</v>
+        <v>48.215</v>
       </c>
       <c r="J34" s="1">
         <v>1.89</v>
@@ -2442,10 +2442,10 @@
         <v>72</v>
       </c>
       <c r="H36" s="1">
-        <v>1.489</v>
+        <v>1.49</v>
       </c>
       <c r="I36" s="1">
-        <v>38.922</v>
+        <v>38.949</v>
       </c>
       <c r="J36" s="1">
         <v>1.61</v>
@@ -2504,10 +2504,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="8">
-        <v>1.70709</v>
+        <v>1.70736</v>
       </c>
       <c r="E41" s="6">
-        <v>1518.09</v>
+        <v>1518.34</v>
       </c>
       <c r="F41" s="6">
         <v>1620.61</v>
@@ -2524,10 +2524,10 @@
         <v>6</v>
       </c>
       <c r="D42" s="8">
-        <v>1.46799</v>
+        <v>1.469</v>
       </c>
       <c r="E42" s="6">
-        <v>281.28</v>
+        <v>281.48</v>
       </c>
       <c r="F42" s="6">
         <v>300.97</v>
@@ -2544,10 +2544,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="8">
-        <v>1.69466</v>
+        <v>1.69806</v>
       </c>
       <c r="E43" s="6">
-        <v>234.3</v>
+        <v>234.77</v>
       </c>
       <c r="F43" s="6">
         <v>252.93</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="10">
-        <v>2119.02</v>
+        <v>2119.94</v>
       </c>
       <c r="F46" s="10">
         <v>2259.86</v>
